--- a/src/attributions/attributions_saliency_traj_427.xlsx
+++ b/src/attributions/attributions_saliency_traj_427.xlsx
@@ -999,571 +999,571 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0002155919646611437</v>
+        <v>1.371781702987074e-12</v>
       </c>
       <c r="B2" t="n">
-        <v>0.004431049339473248</v>
+        <v>4.863828957646366e-12</v>
       </c>
       <c r="C2" t="n">
-        <v>1.266773324459791e-05</v>
+        <v>3.850771698038491e-12</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001341668074019253</v>
+        <v>5.098301988915033e-12</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0009791234042495489</v>
+        <v>4.963931175827607e-12</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001794604118913412</v>
+        <v>9.463952191368641e-12</v>
       </c>
       <c r="G2" t="n">
-        <v>0.000539504864718765</v>
+        <v>5.035548367171572e-12</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00148527161218226</v>
+        <v>1.007415993074107e-13</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004043170250952244</v>
+        <v>3.039085476330694e-12</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001432707766070962</v>
+        <v>2.231860746562675e-12</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002975164679810405</v>
+        <v>1.11990581738719e-11</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000129326363094151</v>
+        <v>2.515593202495614e-12</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003652267158031464</v>
+        <v>4.536168749652569e-12</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0002643074840307236</v>
+        <v>8.093402684150597e-12</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0004955248441547155</v>
+        <v>1.393215837836026e-11</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0005114019731990993</v>
+        <v>4.983654548068595e-12</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0008480206015519798</v>
+        <v>4.355278724471612e-12</v>
       </c>
       <c r="R2" t="n">
-        <v>0.004018250852823257</v>
+        <v>3.913085567380792e-12</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007603877456858754</v>
+        <v>1.994039048464069e-12</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0004378226585686207</v>
+        <v>8.211144437997309e-13</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0005616855341941118</v>
+        <v>7.629478646076215e-13</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0005366375553421676</v>
+        <v>5.507212307714893e-12</v>
       </c>
       <c r="W2" t="n">
-        <v>0.000854567508213222</v>
+        <v>9.466512860059617e-13</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001873340224847198</v>
+        <v>1.869036609508656e-13</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0001038798654917628</v>
+        <v>2.506976830990437e-12</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.764394594123587e-05</v>
+        <v>2.63194262391242e-12</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0009229263523593545</v>
+        <v>1.232298768236162e-12</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.001570932334288955</v>
+        <v>9.074526069810518e-13</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.0001986609422601759</v>
+        <v>1.11714630601778e-12</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.002928568283095956</v>
+        <v>3.955270572869596e-12</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.285470302216709e-05</v>
+        <v>6.910566736906265e-12</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0008877734653651714</v>
+        <v>6.080699312127624e-12</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.0001877165632322431</v>
+        <v>4.57429124960107e-13</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.0005391462473198771</v>
+        <v>1.543601618053669e-12</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.0003313844790682197</v>
+        <v>3.543994308088938e-12</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.0002720585907809436</v>
+        <v>2.663702374991472e-12</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.0002704470243770629</v>
+        <v>2.024060823460627e-12</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.0005772089352831244</v>
+        <v>1.807574923073929e-12</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.0006117236334830523</v>
+        <v>6.55078530482911e-13</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.000120631288154982</v>
+        <v>2.006797072268141e-12</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.0004222419229336083</v>
+        <v>1.921412681737955e-12</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.0006657246267423034</v>
+        <v>2.372006237261193e-12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.0005194254335947335</v>
+        <v>3.942082771324351e-12</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.0002316124737262726</v>
+        <v>1.362396090040519e-12</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.0003898937429767102</v>
+        <v>4.769740375235032e-13</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.0009387093596160412</v>
+        <v>5.969023018914665e-13</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.005089877638965845</v>
+        <v>1.755913123235864e-11</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.0005043558776378632</v>
+        <v>2.201202680416139e-13</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.0006639928906224668</v>
+        <v>9.233304225364503e-13</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.004208380822092295</v>
+        <v>1.47894153521011e-12</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.0004513869062066078</v>
+        <v>9.836272421570591e-13</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.001320406794548035</v>
+        <v>2.602353662423118e-12</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.001225942745804787</v>
+        <v>3.611526008806543e-12</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.0004230733029544353</v>
+        <v>1.067051395159391e-12</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.0003606755926739424</v>
+        <v>7.698806327692542e-13</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.001207426772452891</v>
+        <v>8.211448881967343e-12</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.0001402654743287712</v>
+        <v>2.369884670450073e-12</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.0007447302923537791</v>
+        <v>3.560736558036459e-12</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.0003276608476880938</v>
+        <v>8.490682115724901e-12</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.002289447467774153</v>
+        <v>6.93751783450991e-12</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.0006572995916940272</v>
+        <v>1.448443361778962e-12</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.002574752550572157</v>
+        <v>3.279018332899564e-12</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.0043280771933496</v>
+        <v>2.183935541091864e-12</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.0001045617027557455</v>
+        <v>2.248730281845246e-12</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.0009488529176451266</v>
+        <v>3.972829443893433e-12</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.0006462202873080969</v>
+        <v>9.77725712891786e-13</v>
       </c>
       <c r="BO2" t="n">
-        <v>2.248381497338414e-05</v>
+        <v>1.016854135615919e-12</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.003516587894409895</v>
+        <v>4.22062601881934e-12</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.00030761823290959</v>
+        <v>3.918333105895622e-12</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.0007729268399998546</v>
+        <v>7.236026014489916e-12</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.004547812044621e-05</v>
+        <v>1.906502299781065e-12</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.0008852790342643857</v>
+        <v>2.539047097571689e-12</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.000412003428209573</v>
+        <v>6.606077447221526e-13</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.002670361194759607</v>
+        <v>8.234675961948934e-12</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.001357770408503711</v>
+        <v>1.310407403247449e-13</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.0001117944484576583</v>
+        <v>1.625121912041116e-12</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.001015482121147215</v>
+        <v>3.664678369791341e-12</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.0002613741671666503</v>
+        <v>5.015648812077556e-13</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.830574910854921e-05</v>
+        <v>2.634548395413772e-12</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.001252709655091166</v>
+        <v>2.57796518507436e-12</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.001398856285959482</v>
+        <v>1.380949716557611e-12</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.0001793784758774564</v>
+        <v>1.130757271670946e-12</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.0007701268186792731</v>
+        <v>2.620583871432158e-12</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.0005370479775592685</v>
+        <v>2.770432537893552e-13</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.751057036221027e-05</v>
+        <v>2.39226000120496e-12</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.0004910914576612413</v>
+        <v>1.544862653600487e-12</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.0003472285461612046</v>
+        <v>2.27544654125833e-12</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.0003443769528530538</v>
+        <v>2.237677924898929e-12</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.0005259243189357221</v>
+        <v>3.850287872819019e-13</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.001186338486149907</v>
+        <v>9.819526919016552e-13</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.002002830151468515</v>
+        <v>4.931638430960561e-12</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.0005118179251439869</v>
+        <v>8.427479200601162e-12</v>
       </c>
       <c r="CO2" t="n">
-        <v>3.854477836284786e-05</v>
+        <v>9.871632591224033e-13</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.0003813976072706282</v>
+        <v>7.607426841249598e-12</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.002779203001409769</v>
+        <v>9.465874264980023e-12</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.0005784774548374116</v>
+        <v>1.197436138959673e-12</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.0001099068758776411</v>
+        <v>9.716345566665452e-13</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.001483248081058264</v>
+        <v>1.110264874829014e-12</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.0007950545405037701</v>
+        <v>1.866732029370821e-12</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.0001850002881838009</v>
+        <v>2.011636517085247e-12</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.0008601949666626751</v>
+        <v>2.746455190008601e-12</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.0003729640156961977</v>
+        <v>3.498905267081132e-13</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.0001748163485899568</v>
+        <v>1.916090333273224e-12</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.0003206019755452871</v>
+        <v>1.024838850935406e-12</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.0002414303598925471</v>
+        <v>2.689748814302395e-12</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.0003917056601494551</v>
+        <v>9.965382468876682e-13</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.0002429404703434557</v>
+        <v>9.224634944793308e-13</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.0009039980359375477</v>
+        <v>1.637957456300521e-12</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.001081596477888525</v>
+        <v>1.847366443846754e-12</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.0005145439645275474</v>
+        <v>7.194486976655479e-13</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.001177247380837798</v>
+        <v>1.490015684620094e-12</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.000124861195217818</v>
+        <v>1.954918865676447e-12</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.0005006263963878155</v>
+        <v>1.231814671966147e-12</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.046631950885057e-05</v>
+        <v>4.998460412936057e-13</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.001231518224813044</v>
+        <v>5.319931994929306e-12</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.002388826105743647</v>
+        <v>1.725274003522292e-12</v>
       </c>
       <c r="DM2" t="n">
-        <v>1.776077260728925e-05</v>
+        <v>1.666234424740898e-14</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.0005681615439243615</v>
+        <v>5.007198540345204e-13</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.0002700259792618454</v>
+        <v>1.030107422972382e-12</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.0005627538776025176</v>
+        <v>1.825201881994198e-12</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.0005466952570714056</v>
+        <v>5.666730105990947e-12</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.0008706989465281367</v>
+        <v>4.513116009380314e-12</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.0003892431850545108</v>
+        <v>3.763097906200885e-12</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.0004164804704487324</v>
+        <v>4.978025804069919e-12</v>
       </c>
       <c r="DU2" t="n">
-        <v>4.18387062381953e-05</v>
+        <v>3.65601212498623e-12</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.0009427813347429037</v>
+        <v>1.18420572826905e-12</v>
       </c>
       <c r="DW2" t="n">
-        <v>1.005050580715761e-05</v>
+        <v>2.280349954003613e-12</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.002930293325334787</v>
+        <v>4.046804558122119e-12</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.0004292524245101959</v>
+        <v>3.484245010565434e-12</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.0004067316767759621</v>
+        <v>2.12524030492045e-12</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.0008015744388103485</v>
+        <v>2.385835886492549e-12</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.001133178710006177</v>
+        <v>3.07349545120017e-12</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.00048359643551521</v>
+        <v>5.346966359259797e-13</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.0009428769699297845</v>
+        <v>5.011994725495628e-12</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.0003109491954091936</v>
+        <v>9.828448818693936e-13</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.0001595536014065146</v>
+        <v>3.108760861583737e-12</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.0005954737425781786</v>
+        <v>2.44063368690442e-13</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.0008758426993153989</v>
+        <v>1.832449529571775e-13</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.0001282292068935931</v>
+        <v>2.275447842300937e-12</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.0002988156047649682</v>
+        <v>1.180867252939533e-12</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.000169788661878556</v>
+        <v>7.753749356985418e-13</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.0006944468477740884</v>
+        <v>1.763201780760615e-12</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.0003810201596934348</v>
+        <v>2.770692963255383e-12</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.001269770902581513</v>
+        <v>5.537090968024683e-13</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.0001307915954384953</v>
+        <v>9.205492271235904e-13</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.0008235473069362342</v>
+        <v>2.320727431840558e-13</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.000486317032482475</v>
+        <v>1.638852085723147e-13</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.0004358428122941405</v>
+        <v>3.769975867942699e-13</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.0003601694770622998</v>
+        <v>1.420751103570206e-12</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.0005511401686817408</v>
+        <v>8.246358782458552e-13</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.0005606490303762257</v>
+        <v>2.937841484841608e-13</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.0004592229379341006</v>
+        <v>3.563292673078311e-12</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.001047511119395494</v>
+        <v>4.623339905363011e-12</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.0005463332636281848</v>
+        <v>1.839007895618194e-12</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.001152456388808787</v>
+        <v>3.421572920825344e-12</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.000309952738462016</v>
+        <v>3.003692130090774e-13</v>
       </c>
       <c r="FA2" t="n">
-        <v>9.028844942804426e-05</v>
+        <v>1.816408026593386e-12</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.0002458611270412803</v>
+        <v>1.335340150086795e-12</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.0001265252940356731</v>
+        <v>1.361617199199805e-12</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.0003416935505811125</v>
+        <v>1.187482837755605e-12</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.0002356917248107493</v>
+        <v>8.814062760903463e-13</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.0008704854408279061</v>
+        <v>7.108418671394889e-13</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.000195232845726423</v>
+        <v>2.239754388899673e-12</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.0007206548471003771</v>
+        <v>2.227093943291125e-12</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.0003484574554022402</v>
+        <v>1.072317907212239e-12</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.0006700365920551121</v>
+        <v>1.964367253928789e-12</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.0003096114087384194</v>
+        <v>1.230843660500469e-12</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.0003804451553151011</v>
+        <v>1.675813459355024e-12</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.0004371973918750882</v>
+        <v>1.752982958444504e-12</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.0002216116699855775</v>
+        <v>4.627555283409635e-12</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.0001453793083783239</v>
+        <v>1.802774075854163e-12</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.0006018358981236815</v>
+        <v>3.013363647150213e-12</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.0007240127306431532</v>
+        <v>5.859348596592984e-12</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.0003288724983576685</v>
+        <v>2.243908617943768e-12</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.0001558098010718822</v>
+        <v>1.622914476417936e-12</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.001073061837814748</v>
+        <v>2.544037842801966e-13</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.0006071945535950363</v>
+        <v>1.184293006543935e-13</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.001336415181867778</v>
+        <v>2.465104943089047e-12</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.0009053269168362021</v>
+        <v>2.373371681477221e-12</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.0005174567922949791</v>
+        <v>1.937419408931662e-12</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.0006586218951269984</v>
+        <v>8.791536834466818e-13</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.0005153685924597085</v>
+        <v>1.52031653325585e-13</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.0008570888312533498</v>
+        <v>2.786252402842831e-13</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.001252405811101198</v>
+        <v>1.185265427472437e-12</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.0009455089457333088</v>
+        <v>3.234055818285286e-14</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.0007054050220176578</v>
+        <v>3.529850457067996e-12</v>
       </c>
       <c r="GE2" t="n">
-        <v>5.470159157994203e-05</v>
+        <v>2.706366814680949e-12</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.000588915660046041</v>
+        <v>8.109843092213298e-13</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.0004558238724712282</v>
+        <v>2.649749994074191e-13</v>
       </c>
     </row>
     <row r="3">
@@ -2706,571 +2706,571 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0008425859268754721</v>
+        <v>1.219836676114028e-09</v>
       </c>
       <c r="B5" t="n">
-        <v>0.02685588598251343</v>
+        <v>1.305804131490618e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004895880352705717</v>
+        <v>6.505407879053848e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>7.589894812554121e-05</v>
+        <v>2.502724416597601e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01061203610152006</v>
+        <v>4.593000424435445e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000933332834392786</v>
+        <v>2.125669085195625e-11</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0140829011797905</v>
+        <v>1.470951804805054e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002267923671752214</v>
+        <v>1.725900533600111e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001703810994513333</v>
+        <v>2.149170008625134e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>0.005541552323848009</v>
+        <v>9.655475308179007e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02080560848116875</v>
+        <v>8.666738438023458e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005194226279854774</v>
+        <v>7.96460009055977e-10</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01338686794042587</v>
+        <v>9.215673224538534e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01127468980848789</v>
+        <v>6.749358849589271e-10</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001178568694740534</v>
+        <v>7.311163896517314e-10</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01024965103715658</v>
+        <v>2.161682832735323e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001168751274235547</v>
+        <v>9.89105131132817e-10</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002294735983014107</v>
+        <v>7.491202103082628e-11</v>
       </c>
       <c r="S5" t="n">
-        <v>0.005223594140261412</v>
+        <v>5.552085458049305e-10</v>
       </c>
       <c r="T5" t="n">
-        <v>0.008286934345960617</v>
+        <v>5.685111270636867e-10</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001316059147939086</v>
+        <v>2.109941943384541e-10</v>
       </c>
       <c r="V5" t="n">
-        <v>0.007491767406463623</v>
+        <v>8.580867683072313e-10</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01015791390091181</v>
+        <v>1.850464642627614e-10</v>
       </c>
       <c r="X5" t="n">
-        <v>0.003830863162875175</v>
+        <v>7.232475729423982e-11</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.002300536958500743</v>
+        <v>4.615852422507061e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.000241457368247211</v>
+        <v>7.572548837986304e-11</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.00111926649697125</v>
+        <v>8.283474461912022e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.006173940375447273</v>
+        <v>2.10885442442077e-09</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.005757601000368595</v>
+        <v>1.650115821760778e-09</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.006619761697947979</v>
+        <v>4.746489312701385e-10</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.001675230800174177</v>
+        <v>4.020833110907063e-10</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.003994119819253683</v>
+        <v>7.340484886597665e-10</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.000883965753018856</v>
+        <v>2.111567171114714e-11</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0009918727446347475</v>
+        <v>2.881773430996049e-10</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.005675169173628092</v>
+        <v>1.218116607581976e-09</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.002130649285390973</v>
+        <v>4.631356409490195e-10</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.001817743526771665</v>
+        <v>2.253574410415737e-10</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.004331212025135756</v>
+        <v>5.083157228469304e-10</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0004931694129481912</v>
+        <v>4.827498123471941e-11</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.003041088348254561</v>
+        <v>1.01783470540795e-09</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.003501627361401916</v>
+        <v>3.24246046679022e-10</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.002368035260587931</v>
+        <v>3.257245306809153e-10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.001588982879184186</v>
+        <v>6.732591151248357e-10</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0006744901183992624</v>
+        <v>7.73162200928823e-10</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.0009407157194800675</v>
+        <v>1.494774304333646e-10</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.005920986644923687</v>
+        <v>3.714528684639617e-12</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.01826352439820766</v>
+        <v>1.076728595172938e-09</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.002509862883016467</v>
+        <v>3.642817159033029e-10</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.009475318714976311</v>
+        <v>2.35482688903943e-10</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.007160515524446964</v>
+        <v>9.97340210417974e-10</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.00201483559794724</v>
+        <v>9.450730198423685e-10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0119820749387145</v>
+        <v>3.557200645154523e-10</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.001591176027432084</v>
+        <v>1.140458505410891e-09</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.002186414087191224</v>
+        <v>2.689991840387762e-10</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0006736595532856882</v>
+        <v>1.166143848152501e-10</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.005923304706811905</v>
+        <v>2.019041045464576e-10</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.005408295895904303</v>
+        <v>1.461856052875632e-10</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.006024409085512161</v>
+        <v>4.18331314033793e-10</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.01232339628040791</v>
+        <v>1.261713955535981e-09</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.000345053500495851</v>
+        <v>8.018403163667642e-10</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.0009599190670996904</v>
+        <v>4.576905521247454e-11</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.0009424332529306412</v>
+        <v>3.055682096242407e-10</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.004188835620880127</v>
+        <v>1.960975160031353e-09</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.001633672742173076</v>
+        <v>2.668715803899602e-10</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.005208981689065695</v>
+        <v>1.107465896765802e-09</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.0004920962965115905</v>
+        <v>3.301323381332821e-10</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.0008592422818765044</v>
+        <v>2.183034586433763e-10</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.006853310391306877</v>
+        <v>8.93460194717477e-10</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.002776531968265772</v>
+        <v>1.259825160859762e-10</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.004609922412782907</v>
+        <v>1.073663158379645e-09</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.005511193070560694</v>
+        <v>2.146340744024755e-10</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.003286293707787991</v>
+        <v>1.138358157737329e-10</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.001516449498012662</v>
+        <v>5.416784798484287e-10</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.006962162908166647</v>
+        <v>2.165628648631568e-10</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.004377250093966722</v>
+        <v>3.412312099548842e-11</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.00609309459105134</v>
+        <v>5.738512998121337e-10</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.005572014488279819</v>
+        <v>8.349612112823479e-10</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.002247546100988984</v>
+        <v>2.292877554488371e-10</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.006364106666296721</v>
+        <v>1.115952885655247e-09</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.004661426413804293</v>
+        <v>3.434172390903711e-10</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.001838328782469034</v>
+        <v>9.532331174399999e-11</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.001373413833789527</v>
+        <v>1.001686164570081e-10</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.005083187948912382</v>
+        <v>5.931677371506794e-11</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.0009264855762012303</v>
+        <v>2.415484201545581e-10</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.001298598712310195</v>
+        <v>8.625204023227084e-11</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.0014182657469064</v>
+        <v>1.255694992430278e-10</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.00119773845653981</v>
+        <v>9.161834485515996e-11</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.00266182073391974</v>
+        <v>3.53813950360049e-10</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.001317038317210972</v>
+        <v>9.112960386303826e-11</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0007579228840768337</v>
+        <v>2.61770938259076e-10</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.005298933945596218</v>
+        <v>1.089444645607784e-09</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.003044716082513332</v>
+        <v>1.549155137503533e-09</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.000355864962330088</v>
+        <v>1.052022025049837e-09</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.006378103047609329</v>
+        <v>1.311829644912166e-09</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.007154806982725859</v>
+        <v>7.405089319512115e-10</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.0009367531165480614</v>
+        <v>2.728035852772592e-10</v>
       </c>
       <c r="CS5" t="n">
-        <v>5.403249815572053e-05</v>
+        <v>2.041018187792787e-10</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0003221235238015652</v>
+        <v>5.717810114269639e-10</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.002809061203151941</v>
+        <v>9.893741381716836e-10</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.001629790756851435</v>
+        <v>2.101447488245256e-11</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.004658473655581474</v>
+        <v>1.752759326567599e-10</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.0006471340311691165</v>
+        <v>2.688785583071507e-10</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0004666517779696733</v>
+        <v>1.35509464760375e-10</v>
       </c>
       <c r="CZ5" t="n">
-        <v>4.63991891592741e-05</v>
+        <v>4.36496047639956e-11</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.001465707318857312</v>
+        <v>4.631038608149396e-12</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.003392324782907963</v>
+        <v>1.408058253327127e-10</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.00250915577635169</v>
+        <v>6.224508408703144e-11</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.0005474092904478312</v>
+        <v>3.258826819507732e-10</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.006463177502155304</v>
+        <v>3.003807202972553e-10</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.003587478073313832</v>
+        <v>3.239335466531656e-10</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.001610424951650202</v>
+        <v>1.813052485921673e-09</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.007386378478258848</v>
+        <v>2.029207246678766e-09</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.001375742140226066</v>
+        <v>8.098292592073619e-10</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.004147060215473175</v>
+        <v>3.008689963834854e-10</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.00104322237893939</v>
+        <v>1.23090870829401e-09</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.005766779184341431</v>
+        <v>6.984587908043238e-11</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.003256018972024322</v>
+        <v>3.229138623161987e-10</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.005069232080131769</v>
+        <v>2.842107105216485e-10</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0004720048746094108</v>
+        <v>4.545582799053705e-10</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.001993652433156967</v>
+        <v>8.879359747471227e-11</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.001028117490932345</v>
+        <v>1.432338692097801e-10</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.002002374734729528</v>
+        <v>9.856161442556299e-10</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.0005976968677714467</v>
+        <v>5.529200985954219e-10</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.001688213902525604</v>
+        <v>7.625259312860067e-10</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0004654473159462214</v>
+        <v>4.734885261648003e-10</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.00338881416246295</v>
+        <v>7.948047775485634e-10</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.001279383897781372</v>
+        <v>5.919916640229061e-11</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.01180959213525057</v>
+        <v>1.912199731890496e-09</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.0006517812144011259</v>
+        <v>2.376705776629962e-10</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.000729691528249532</v>
+        <v>1.144207506520445e-09</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.003188299247995019</v>
+        <v>8.62765081599548e-10</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.002100627869367599</v>
+        <v>9.876141016107454e-10</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0007929700659587979</v>
+        <v>7.598082163440267e-10</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.002011274453252554</v>
+        <v>4.393514163592016e-10</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.002512488281354308</v>
+        <v>1.618716938267539e-09</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.001986958784982562</v>
+        <v>4.743522796779587e-10</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.002625858876854181</v>
+        <v>1.168819041552638e-09</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.0004221161943860352</v>
+        <v>4.00027788671764e-10</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.0009546263609081507</v>
+        <v>2.011050770356348e-10</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.001350143691524863</v>
+        <v>1.365716706391851e-10</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.001036546658724546</v>
+        <v>6.395754481580695e-10</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.005320754833519459</v>
+        <v>2.201535898027629e-10</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.000674055831041187</v>
+        <v>6.020292597774812e-11</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.001303532277233899</v>
+        <v>3.401645909395512e-10</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.002335686702281237</v>
+        <v>3.132474557521192e-10</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.003084048861637712</v>
+        <v>6.122822249210458e-10</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.002623733133077621</v>
+        <v>1.98196722922539e-10</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.0009541737381368876</v>
+        <v>4.234852191142835e-10</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.003406671807169914</v>
+        <v>3.061298436968229e-10</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.0005877787480130792</v>
+        <v>5.589740892375517e-10</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.001580771873705089</v>
+        <v>6.448987455165422e-10</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.0007428213721141219</v>
+        <v>6.873273061813734e-10</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.0002662597980815917</v>
+        <v>1.443273695000968e-10</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.003145220689475536</v>
+        <v>2.142398897175823e-10</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.005432725418359041</v>
+        <v>2.487815509155666e-12</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.0002507623285055161</v>
+        <v>2.529712550547458e-10</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.0006586817326024175</v>
+        <v>3.458471564687926e-10</v>
       </c>
       <c r="FB5" t="n">
-        <v>1.077089109458029e-05</v>
+        <v>1.552852707531471e-10</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0006096095312386751</v>
+        <v>8.172301724229669e-11</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.003348905127495527</v>
+        <v>2.756171402218399e-10</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.001574693247675896</v>
+        <v>1.17207743510761e-10</v>
       </c>
       <c r="FF5" t="n">
-        <v>4.848162643611431e-05</v>
+        <v>3.326399711234274e-10</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.001604394055902958</v>
+        <v>7.63947294313283e-10</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.0006203379016369581</v>
+        <v>1.177141051300623e-09</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.00199664244428277</v>
+        <v>1.297346813311506e-10</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.0007904820377007127</v>
+        <v>4.526460456455439e-11</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.005112519953399897</v>
+        <v>1.10387622653807e-10</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.00273597170598805</v>
+        <v>2.816943900363356e-10</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0005067643360234797</v>
+        <v>4.84863704741656e-10</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.002490804065018892</v>
+        <v>8.209979363016373e-10</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.005650835111737251</v>
+        <v>1.765606438830503e-09</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.00341459084302187</v>
+        <v>6.376345007552686e-10</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.00618450902402401</v>
+        <v>2.549804367646402e-09</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.0002122103469446301</v>
+        <v>1.642082025909986e-10</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.0009831320494413376</v>
+        <v>1.601383692317881e-09</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.005159115418791771</v>
+        <v>1.938673666046498e-09</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.00219886633567512</v>
+        <v>1.281965644750471e-09</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0008123354054987431</v>
+        <v>1.204079058680918e-09</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.007552535273134708</v>
+        <v>2.685143218883468e-09</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.003048954764381051</v>
+        <v>3.632287248755972e-10</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.004554158542305231</v>
+        <v>2.271581672763645e-10</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.001430742908269167</v>
+        <v>2.95060281763071e-10</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.002065435284748673</v>
+        <v>1.128172222308876e-09</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.002875034231692553</v>
+        <v>1.242462022155166e-09</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.005904316436499357</v>
+        <v>1.19262622000349e-09</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.002498074201866984</v>
+        <v>5.11364617317156e-10</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.0003045268822461367</v>
+        <v>1.432753776731133e-10</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.008910414762794971</v>
+        <v>5.106893241624277e-10</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.0003177616745233536</v>
+        <v>4.597017766450051e-10</v>
       </c>
     </row>
     <row r="6">
@@ -3844,1140 +3844,1140 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.003100740257650614</v>
+        <v>0.03511403501033783</v>
       </c>
       <c r="B7" t="n">
-        <v>0.07922438532114029</v>
+        <v>0.1425357013940811</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008488338440656662</v>
+        <v>0.0843995213508606</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03961693495512009</v>
+        <v>0.05636585876345634</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008573355153203011</v>
+        <v>0.03104731813073158</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009154121391475201</v>
+        <v>0.01470640674233437</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003490533214062452</v>
+        <v>0.07898053526878357</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001792190741980448</v>
+        <v>0.05167868733406067</v>
       </c>
       <c r="I7" t="n">
-        <v>0.004415962845087051</v>
+        <v>0.05961873009800911</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007451680488884449</v>
+        <v>0.04034922271966934</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06366740167140961</v>
+        <v>0.2125916182994843</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002032344695180655</v>
+        <v>0.1017440780997276</v>
       </c>
       <c r="M7" t="n">
-        <v>0.04579509794712067</v>
+        <v>0.09216277301311493</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01247865334153175</v>
+        <v>0.06391410529613495</v>
       </c>
       <c r="O7" t="n">
-        <v>0.004422431811690331</v>
+        <v>0.00614105723798275</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0008278093300759792</v>
+        <v>0.02688082307577133</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01144849509000778</v>
+        <v>0.1100394502282143</v>
       </c>
       <c r="R7" t="n">
-        <v>0.00327346078120172</v>
+        <v>0.04281838238239288</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003381264396011829</v>
+        <v>0.008462998084723949</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01865343935787678</v>
+        <v>0.0377487912774086</v>
       </c>
       <c r="U7" t="n">
-        <v>0.005703610833734274</v>
+        <v>0.05632265284657478</v>
       </c>
       <c r="V7" t="n">
-        <v>0.002869413234293461</v>
+        <v>0.004406247287988663</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01526954770088196</v>
+        <v>0.02882584184408188</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01526314206421375</v>
+        <v>0.0217729676514864</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.008336039260029793</v>
+        <v>0.01403964497148991</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0004005094524472952</v>
+        <v>0.02060029655694962</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002889523981139064</v>
+        <v>0.0615142397582531</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01148653868585825</v>
+        <v>0.02870634943246841</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.01490576565265656</v>
+        <v>0.004350733011960983</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.002108669141307473</v>
+        <v>0.01059051975607872</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.002456111833453178</v>
+        <v>0.1166495978832245</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.008868776261806488</v>
+        <v>0.05793662741780281</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.01387561298906803</v>
+        <v>0.1280661225318909</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.004942834377288818</v>
+        <v>0.03314683586359024</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.002104293555021286</v>
+        <v>0.01016112975776196</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.002508980222046375</v>
+        <v>0.005428086966276169</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.002065436216071248</v>
+        <v>0.01287163607776165</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.007628517691046</v>
+        <v>0.1029088646173477</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.001735749538056552</v>
+        <v>0.04221717640757561</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0003588430117815733</v>
+        <v>0.01023972034454346</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.00127931241877377</v>
+        <v>0.06122739240527153</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.007668221369385719</v>
+        <v>0.04160183295607567</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.004838948603719473</v>
+        <v>0.0138947619125247</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.001441145897842944</v>
+        <v>0.02973607182502747</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.001020223135128617</v>
+        <v>0.01399421039968729</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.008981221355497837</v>
+        <v>0.002425170503556728</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.04395207762718201</v>
+        <v>0.1587569266557693</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.001252566929906607</v>
+        <v>0.04208001866936684</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.01221360266208649</v>
+        <v>0.04247255623340607</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.002865887712687254</v>
+        <v>0.05415231734514236</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.0004519675858318806</v>
+        <v>0.03222785145044327</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.00281657068990171</v>
+        <v>0.003274489194154739</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.004371279384940863</v>
+        <v>0.05132364481687546</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.003723202738910913</v>
+        <v>0.02718518488109112</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.002795969601720572</v>
+        <v>0.01183006353676319</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.01720991730690002</v>
+        <v>0.1357647329568863</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.01014483440667391</v>
+        <v>0.09575876593589783</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.008727729320526123</v>
+        <v>0.05405241250991821</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.02078503556549549</v>
+        <v>0.08415094017982483</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.004989166744053364</v>
+        <v>0.04069073870778084</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.00854277890175581</v>
+        <v>0.01777319423854351</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.005988303106278181</v>
+        <v>0.042880579829216</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.0003457042621448636</v>
+        <v>0.06358311325311661</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.006372741423547268</v>
+        <v>0.004322235938161612</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.00706573249772191</v>
+        <v>0.05279216915369034</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.001061136368662119</v>
+        <v>0.02090157195925713</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.007407818920910358</v>
+        <v>0.02787747606635094</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.006799886003136635</v>
+        <v>0.02234891802072525</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.006992226932197809</v>
+        <v>0.04561727121472359</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.001607946236617863</v>
+        <v>0.02064330503344536</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.006959615275263786</v>
+        <v>0.02114961482584476</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.008490923792123795</v>
+        <v>0.004249823279678822</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.006713859271258116</v>
+        <v>0.01498854346573353</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.02321001887321472</v>
+        <v>0.1043921038508415</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.005642067175358534</v>
+        <v>0.00638915179297328</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.004659474361687899</v>
+        <v>0.007881037890911102</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.008409378118813038</v>
+        <v>0.01486609131097794</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.004999835509806871</v>
+        <v>0.03857720270752907</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.0001074419124051929</v>
+        <v>0.01751736365258694</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.001300318632274866</v>
+        <v>0.06198808550834656</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.001146940747275949</v>
+        <v>0.03849920257925987</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.001581042190082371</v>
+        <v>0.007759994827210903</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.01280754338949919</v>
+        <v>0.05383839085698128</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.0009196438477374613</v>
+        <v>0.01752477884292603</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.004174388945102692</v>
+        <v>0.02302651479840279</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.003393570194020867</v>
+        <v>0.007179336156696081</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.002095500705763698</v>
+        <v>0.0002328015398234129</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.002247847616672516</v>
+        <v>0.009171990677714348</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.001131002674810588</v>
+        <v>0.01134961657226086</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.0008860751986503601</v>
+        <v>0.006882444489747286</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.009574484080076218</v>
+        <v>0.05342691019177437</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0009180603665299714</v>
+        <v>0.01250604260712862</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0014261978212744</v>
+        <v>0.01133470330387354</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.01240950915962458</v>
+        <v>0.09777235984802246</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.01270218379795551</v>
+        <v>0.07877523452043533</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.008272504433989525</v>
+        <v>0.05171064287424088</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.00460236007347703</v>
+        <v>0.03176157549023628</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.005010878201574087</v>
+        <v>0.02371570095419884</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.0009036865085363388</v>
+        <v>0.0399082787334919</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.0006328020244836807</v>
+        <v>0.007524812128394842</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.01269289199262857</v>
+        <v>0.06149650365114212</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.002820648951455951</v>
+        <v>0.01952767930924892</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.00528836390003562</v>
+        <v>0.02825318276882172</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.003338920418173075</v>
+        <v>0.00446194875985384</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.004682315979152918</v>
+        <v>0.01264428533613682</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.003243695246055722</v>
+        <v>0.006671207025647163</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.001564135192893445</v>
+        <v>0.01072204858064651</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.001555827329866588</v>
+        <v>0.01565102301537991</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.004471981432288885</v>
+        <v>0.006205518264323473</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.02825818210840225</v>
+        <v>0.04856349900364876</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.001594287808984518</v>
+        <v>0.0834573358297348</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.001892245374619961</v>
+        <v>0.01632988452911377</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.00604261364787817</v>
+        <v>0.0171484611928463</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.006677206605672836</v>
+        <v>0.1038813292980194</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.001133104786276817</v>
+        <v>0.03111000172793865</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.0008350361604243517</v>
+        <v>0.04734372347593307</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.005966129247099161</v>
+        <v>0.008488357998430729</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.0003470191149972379</v>
+        <v>0.013545504771173</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.005718579050153494</v>
+        <v>0.009998021647334099</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.006581519264727831</v>
+        <v>0.002138381591066718</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.0008712796261534095</v>
+        <v>0.008067825809121132</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.006277271546423435</v>
+        <v>0.008922696113586426</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.005449147894978523</v>
+        <v>0.01724112965166569</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.00179557385854423</v>
+        <v>0.01265889033675194</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.005268468521535397</v>
+        <v>0.019920464605093</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.001144124544225633</v>
+        <v>0.07109368592500687</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.000305098423268646</v>
+        <v>0.006730254273861647</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.008190032094717026</v>
+        <v>0.03781672939658165</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.005294985137879848</v>
+        <v>0.0248107798397541</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.001513347029685974</v>
+        <v>0.01218717452138662</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.0009304403210990131</v>
+        <v>0.04675071313977242</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.008219517767429352</v>
+        <v>0.07698211073875427</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0007698491681367159</v>
+        <v>0.01184937730431557</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.002348256297409534</v>
+        <v>0.03505463898181915</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.004595794714987278</v>
+        <v>0.03040475584566593</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.001576674869284034</v>
+        <v>0.01877415925264359</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.005272373557090759</v>
+        <v>0.01781151629984379</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.003836165182292461</v>
+        <v>0.02047738805413246</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.00422554649412632</v>
+        <v>0.02362819202244282</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.004007249139249325</v>
+        <v>0.008004996925592422</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.006108065601438284</v>
+        <v>0.003911660984158516</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.003351205261424184</v>
+        <v>0.00530196912586689</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.002527350559830666</v>
+        <v>0.002114917384460568</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.002788611687719822</v>
+        <v>0.004393937066197395</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.0006955937133170664</v>
+        <v>0.01417561806738377</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.01423454843461514</v>
+        <v>0.06305966526269913</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.003999031614512205</v>
+        <v>0.01295656897127628</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.0001956442429218441</v>
+        <v>0.006284252740442753</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.003674129955470562</v>
+        <v>0.04645639285445213</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.005515723489224911</v>
+        <v>0.03091880306601524</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.003438486251980066</v>
+        <v>0.02465830370783806</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.002695849165320396</v>
+        <v>0.009645754471421242</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.0001202750718221068</v>
+        <v>0.03733591735363007</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.00152377865742892</v>
+        <v>0.007826549001038074</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.01443052850663662</v>
+        <v>0.07165274024009705</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.00122794636990875</v>
+        <v>0.001466680318117142</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.004678108729422092</v>
+        <v>0.02649124711751938</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.005098272580653429</v>
+        <v>0.001457587350159883</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.005922359880059958</v>
+        <v>0.01026830263435841</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.001308126840740442</v>
+        <v>0.005359003785997629</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.0006572920829057693</v>
+        <v>0.009313549846410751</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.000817798834759742</v>
+        <v>0.01554016210138798</v>
       </c>
       <c r="FG7" t="n">
-        <v>2.463313285261393e-05</v>
+        <v>0.009929564781486988</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.001088102231733501</v>
+        <v>0.0462518036365509</v>
       </c>
       <c r="FI7" t="n">
-        <v>8.333189180120826e-05</v>
+        <v>0.02858689613640308</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.006204712670296431</v>
+        <v>0.03457493707537651</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.0002618784783408046</v>
+        <v>0.04062547534704208</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.009673863649368286</v>
+        <v>0.02463604882359505</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.002709066728129983</v>
+        <v>0.001931704115122557</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.001737050013616681</v>
+        <v>0.01142855174839497</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.005268743727356195</v>
+        <v>0.06493820995092392</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.0001237266696989536</v>
+        <v>0.0005282200872898102</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.01809284463524818</v>
+        <v>0.02185515314340591</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.007217438891530037</v>
+        <v>0.003454487305134535</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.005738151259720325</v>
+        <v>0.04120693355798721</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.001055446919053793</v>
+        <v>0.1205346509814262</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.001301060430705547</v>
+        <v>0.05896605178713799</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.002532575745135546</v>
+        <v>0.04316567629575729</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.0005202849861234426</v>
+        <v>0.02603334374725819</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.00684030819684267</v>
+        <v>0.02440598048269749</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.004701237659901381</v>
+        <v>0.008483720943331718</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.002421608427539468</v>
+        <v>0.07499882578849792</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.0008257150184363127</v>
+        <v>0.06262166053056717</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.007650945335626602</v>
+        <v>0.00301697850227356</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.01786171272397041</v>
+        <v>0.02069110050797462</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.009313403628766537</v>
+        <v>0.0284188911318779</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.005942749790847301</v>
+        <v>0.0433381088078022</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.001344715477898717</v>
+        <v>0.01391819026321173</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.002696404000744224</v>
+        <v>0.003930186852812767</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0006718981312587857</v>
+        <v>0.2798917889595032</v>
       </c>
       <c r="B8" t="n">
-        <v>0.004422097001224756</v>
+        <v>0.6416265368461609</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0003675504704006016</v>
+        <v>0.1826338320970535</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002420727163553238</v>
+        <v>0.02410733141005039</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0007480846834369004</v>
+        <v>0.06923536956310272</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003172011114656925</v>
+        <v>0.3713849484920502</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001572027977090329</v>
+        <v>0.05468767136335373</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001013776520267129</v>
+        <v>0.02915884926915169</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0002944905136246234</v>
+        <v>0.1281826943159103</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001480837119743228</v>
+        <v>0.1471278071403503</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003353816689923406</v>
+        <v>0.8609853982925415</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001347602810710669</v>
+        <v>0.08685851097106934</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002228487282991409</v>
+        <v>0.1986826062202454</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0007277789991348982</v>
+        <v>0.2032337486743927</v>
       </c>
       <c r="O8" t="n">
-        <v>0.003499681828543544</v>
+        <v>0.3901436626911163</v>
       </c>
       <c r="P8" t="n">
-        <v>5.865964340046048e-06</v>
+        <v>0.1907362788915634</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.85994028672576e-05</v>
+        <v>0.2474459558725357</v>
       </c>
       <c r="R8" t="n">
-        <v>0.000242151363636367</v>
+        <v>0.1383112818002701</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0003556511364877224</v>
+        <v>0.01660279743373394</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0006270744488574564</v>
+        <v>0.2408761233091354</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0003454932302702218</v>
+        <v>0.00735023058950901</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0004032735887449235</v>
+        <v>0.1972301006317139</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0002480974071659148</v>
+        <v>0.1604640036821365</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0002865451097022742</v>
+        <v>0.02249427139759064</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0005781402578577399</v>
+        <v>0.02256932109594345</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0003987872041761875</v>
+        <v>0.1119615212082863</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0005214111297391355</v>
+        <v>0.06393006443977356</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.928897108882666e-05</v>
+        <v>0.0266529880464077</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.000472966959932819</v>
+        <v>0.0799553245306015</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0001255904935533181</v>
+        <v>0.1056853085756302</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.960829104064032e-05</v>
+        <v>0.3344570398330688</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0002168655628338456</v>
+        <v>0.3394309282302856</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0001618768146727234</v>
+        <v>0.1030348390340805</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0002374803298152983</v>
+        <v>0.05913543701171875</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0003531062684487551</v>
+        <v>0.2091717720031738</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0001517580240033567</v>
+        <v>0.01652182638645172</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0003982065245509148</v>
+        <v>0.03865605220198631</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0007065099198371172</v>
+        <v>0.3125362694263458</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0002812767634168267</v>
+        <v>0.04509788006544113</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.148631943389773e-05</v>
+        <v>0.116992712020874</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0003043464093934745</v>
+        <v>0.1696757525205612</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0005743216024711728</v>
+        <v>0.07971753925085068</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.349728649482131e-05</v>
+        <v>0.06392856687307358</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.0002634511620271951</v>
+        <v>0.2053444683551788</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.0006563109345734119</v>
+        <v>0.0252989623695612</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0002782000810839236</v>
+        <v>0.1078950241208076</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.002693807706236839</v>
+        <v>0.8903111815452576</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0002622753381729126</v>
+        <v>0.02771646529436111</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0002156839182134718</v>
+        <v>0.001056637614965439</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0002193036343669519</v>
+        <v>0.09115311503410339</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.001736431149765849</v>
+        <v>0.3499773740768433</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.269054625183344e-05</v>
+        <v>0.002395778894424438</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.0006968305096961558</v>
+        <v>0.06644643843173981</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.0009825588203966618</v>
+        <v>0.05625644326210022</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.00079653988359496</v>
+        <v>0.1100752428174019</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0007992616738192737</v>
+        <v>0.3169215023517609</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.001256183721125126</v>
+        <v>0.06583990156650543</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.0008294163853861392</v>
+        <v>0.1685921251773834</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.001396937062963843</v>
+        <v>0.3287525475025177</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.0009484637994319201</v>
+        <v>0.1291180700063705</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0001799573510652408</v>
+        <v>0.1167596653103828</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.000902047730050981</v>
+        <v>0.1004460602998734</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0002000411768676713</v>
+        <v>0.1323859840631485</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0001365068892482668</v>
+        <v>0.1178444623947144</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0004806399228982627</v>
+        <v>0.0047183558344841</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.0005719618056900799</v>
+        <v>0.01693058013916016</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.0006321059190668166</v>
+        <v>0.06869480013847351</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0003691210295073688</v>
+        <v>0.04990985244512558</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.654937220038846e-05</v>
+        <v>0.07940300554037094</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.0003830374917015433</v>
+        <v>0.0387599766254425</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.0001569732266943902</v>
+        <v>0.06504998356103897</v>
       </c>
       <c r="BT8" t="n">
-        <v>5.314248846843839e-05</v>
+        <v>0.1104638203978539</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.0002236810105387121</v>
+        <v>0.08460827171802521</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.001326624304056168</v>
+        <v>0.614870548248291</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.0007024133810773492</v>
+        <v>0.03822300210595131</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0006337934755720198</v>
+        <v>0.1097452640533447</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0005288782995194197</v>
+        <v>0.09107086062431335</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0006119006429798901</v>
+        <v>0.236125648021698</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0003377164539415389</v>
+        <v>0.06520237773656845</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0003968692326452583</v>
+        <v>0.01997776702046394</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0007085870020091534</v>
+        <v>0.01342551410198212</v>
       </c>
       <c r="CD8" t="n">
-        <v>5.340677307685837e-05</v>
+        <v>0.008788146078586578</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0006983906496316195</v>
+        <v>0.2379602640867233</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0006215999601408839</v>
+        <v>0.01658105663955212</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0003976959269493818</v>
+        <v>0.02636783942580223</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0002679855388123542</v>
+        <v>0.01894473284482956</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0005853399052284658</v>
+        <v>0.1111967712640762</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.0002213565167039633</v>
+        <v>0.03602541610598564</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0001866226812126115</v>
+        <v>0.03543243929743767</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0003896079724654555</v>
+        <v>0.01997740752995014</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.0004583009867928922</v>
+        <v>0.204246923327446</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0001593440101714805</v>
+        <v>0.3893515467643738</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.0002836801286321133</v>
+        <v>0.1089465618133545</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.0002842702378984541</v>
+        <v>0.3311469256877899</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0001825760555220768</v>
+        <v>0.3365259766578674</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.0001422310306224972</v>
+        <v>0.2676473557949066</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.0006166109815239906</v>
+        <v>0.01113627105951309</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.0006542552728205919</v>
+        <v>0.07860661298036575</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.0001878602197393775</v>
+        <v>0.0952116847038269</v>
       </c>
       <c r="CV8" t="n">
-        <v>3.448427742114291e-05</v>
+        <v>0.03147046267986298</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.0006378691759891808</v>
+        <v>0.2143807411193848</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.0005703656934201717</v>
+        <v>0.01130492798984051</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.000608629547059536</v>
+        <v>0.03276100009679794</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.000248892669333145</v>
+        <v>0.01061361283063889</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0006693360046483576</v>
+        <v>0.1035231649875641</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.0001850796688813716</v>
+        <v>0.01679578796029091</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.0004243878356646746</v>
+        <v>0.05602634698152542</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.0002584281610324979</v>
+        <v>0.007806011009961367</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.0004314366378821433</v>
+        <v>0.071403868496418</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.0005138700362294912</v>
+        <v>0.03010072559118271</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0001832326815929264</v>
+        <v>0.09360150992870331</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.001220656442455947</v>
+        <v>0.01817552000284195</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.0001508539135102183</v>
+        <v>0.1568823605775833</v>
       </c>
       <c r="DJ8" t="n">
-        <v>6.3459032389801e-05</v>
+        <v>0.005631798878312111</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.000460976327303797</v>
+        <v>0.1551687121391296</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.0006629655254073441</v>
+        <v>0.1100033074617386</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0001674706727499142</v>
+        <v>0.08049272000789642</v>
       </c>
       <c r="DN8" t="n">
-        <v>9.554217103868723e-05</v>
+        <v>0.02016391977667809</v>
       </c>
       <c r="DO8" t="n">
-        <v>4.112439637538046e-05</v>
+        <v>0.1122355386614799</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.0003511031973175704</v>
+        <v>0.01840642094612122</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0003642577794380486</v>
+        <v>0.09424546360969543</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0001242790167452767</v>
+        <v>0.1025948449969292</v>
       </c>
       <c r="DS8" t="n">
-        <v>9.406395838595927e-05</v>
+        <v>0.02671878412365913</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.0003794822259806097</v>
+        <v>0.03210925310850143</v>
       </c>
       <c r="DU8" t="n">
-        <v>2.501398557797074e-05</v>
+        <v>0.1057291701436043</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.0007118863286450505</v>
+        <v>0.04649106413125992</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0002005862916121259</v>
+        <v>0.1190664768218994</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.0004197345697320998</v>
+        <v>0.07933986186981201</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.0008431457099504769</v>
+        <v>0.1328199207782745</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.0001020823401631787</v>
+        <v>0.03624388948082924</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.0001626282028155401</v>
+        <v>0.0695137083530426</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0003860350989270955</v>
+        <v>0.1101883202791214</v>
       </c>
       <c r="EC8" t="n">
-        <v>4.795296990778297e-05</v>
+        <v>0.125725269317627</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0003364286967553198</v>
+        <v>0.04077361151576042</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.0001154388737631962</v>
+        <v>0.01469101198017597</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.000301342224702239</v>
+        <v>0.002836201339960098</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0005217015859670937</v>
+        <v>0.03857846558094025</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0004243665316607803</v>
+        <v>0.05351844429969788</v>
       </c>
       <c r="EI8" t="n">
-        <v>2.233416489616502e-05</v>
+        <v>0.06301625072956085</v>
       </c>
       <c r="EJ8" t="n">
-        <v>3.638601629063487e-05</v>
+        <v>0.07999429106712341</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.0005930393235757947</v>
+        <v>0.06444592773914337</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.0003361268900334835</v>
+        <v>0.03095788136124611</v>
       </c>
       <c r="EM8" t="n">
-        <v>8.59647843753919e-05</v>
+        <v>0.0343470573425293</v>
       </c>
       <c r="EN8" t="n">
-        <v>8.71296288096346e-05</v>
+        <v>0.004927951376885176</v>
       </c>
       <c r="EO8" t="n">
-        <v>3.49550973623991e-05</v>
+        <v>0.01939243450760841</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0002799822541419417</v>
+        <v>0.06615245342254639</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0005772802978754044</v>
+        <v>0.01496230065822601</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.0003355908556841314</v>
+        <v>0.0440918356180191</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.0004308813659008592</v>
+        <v>0.0877738818526268</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0004988180589862168</v>
+        <v>0.009800086729228497</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.000453597487648949</v>
+        <v>0.004987749271094799</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.0007593510672450066</v>
+        <v>0.01068159751594067</v>
       </c>
       <c r="EW8" t="n">
-        <v>5.733109719585627e-05</v>
+        <v>0.009106490761041641</v>
       </c>
       <c r="EX8" t="n">
-        <v>8.252181578427553e-05</v>
+        <v>0.01226246356964111</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.000615455734077841</v>
+        <v>0.2389857023954391</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.0004466557875275612</v>
+        <v>0.01909765042364597</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.0004964710678905249</v>
+        <v>0.0469224601984024</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.0003286672581452876</v>
+        <v>0.01539510209113359</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.0005265045911073685</v>
+        <v>0.08698112517595291</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.0003647086850833148</v>
+        <v>0.05269003659486771</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.0002480171388015151</v>
+        <v>0.04828595370054245</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.0004365927306935191</v>
+        <v>0.01970270276069641</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.0001193521602544934</v>
+        <v>0.07142190635204315</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.0003136432496830821</v>
+        <v>0.2595370709896088</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.0006037569837644696</v>
+        <v>0.05797929689288139</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.000709940679371357</v>
+        <v>0.1900433748960495</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.0001649264595471323</v>
+        <v>0.0899837464094162</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.0004662069259211421</v>
+        <v>0.1710473746061325</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.000314451550366357</v>
+        <v>0.1493067145347595</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.0002856584906112403</v>
+        <v>0.2501856982707977</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.0004328527138568461</v>
+        <v>0.09127004444599152</v>
       </c>
       <c r="FP8" t="n">
-        <v>9.881414007395506e-05</v>
+        <v>0.1732011735439301</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.0009436405962333083</v>
+        <v>0.528892457485199</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.0002169909421354532</v>
+        <v>0.0007764138281345367</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.001019480754621327</v>
+        <v>0.1612812429666519</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.0007514557801187038</v>
+        <v>0.02261416614055634</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.0002724934020079672</v>
+        <v>0.1399307996034622</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.0003075335407629609</v>
+        <v>0.1166634783148766</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.0003089414094574749</v>
+        <v>0.0615144744515419</v>
       </c>
       <c r="FX8" t="n">
-        <v>5.120893911225721e-05</v>
+        <v>0.03173717111349106</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.0009216847829520702</v>
+        <v>0.0434536300599575</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.0001700313296169043</v>
+        <v>0.116861566901207</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.0001534700422780588</v>
+        <v>0.01009576767683029</v>
       </c>
       <c r="GB8" t="n">
-        <v>5.33625679963734e-05</v>
+        <v>0.1169818416237831</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.0003001303994096816</v>
+        <v>0.04750006645917892</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.0003577266179490834</v>
+        <v>0.03444156050682068</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.002076083794236183</v>
+        <v>0.04343162477016449</v>
       </c>
       <c r="GF8" t="n">
-        <v>8.276202424895018e-05</v>
+        <v>0.104673333466053</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.0003869059728458524</v>
+        <v>0.1047313883900642</v>
       </c>
     </row>
     <row r="9">
@@ -5551,2278 +5551,2278 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.04628117382526398</v>
+        <v>2.173717348341597e-06</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2185528725385666</v>
+        <v>7.133555754990084e-06</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01737931184470654</v>
+        <v>2.35297932249523e-07</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0763181671500206</v>
+        <v>1.945310259543476e-06</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1074501797556877</v>
+        <v>2.710007265704917e-06</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00193905271589756</v>
+        <v>1.07066068721906e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02031820826232433</v>
+        <v>1.007187620416516e-06</v>
       </c>
       <c r="H10" t="n">
-        <v>0.02894157543778419</v>
+        <v>2.990987240991672e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>0.008238951675593853</v>
+        <v>6.272714472288499e-07</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0405396930873394</v>
+        <v>4.088256446266314e-06</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1619797796010971</v>
+        <v>7.444542916346109e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01472830772399902</v>
+        <v>1.115429085984943e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>0.09728193283081055</v>
+        <v>1.637625246075913e-06</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1137116700410843</v>
+        <v>5.168947609490715e-06</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02993317320942879</v>
+        <v>1.219221530845971e-06</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01068350486457348</v>
+        <v>4.953480129188392e-06</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1118756681680679</v>
+        <v>6.192088221723679e-06</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01518923230469227</v>
+        <v>1.230828274856322e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>0.003473075572401285</v>
+        <v>3.23877338814782e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.07189731299877167</v>
+        <v>7.426974661939312e-06</v>
       </c>
       <c r="U10" t="n">
-        <v>0.005563874263316393</v>
+        <v>2.525733179936651e-06</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01093904860317707</v>
+        <v>3.197026444468065e-06</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02719856612384319</v>
+        <v>1.704514488665154e-06</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0226349588483572</v>
+        <v>1.249559431926173e-06</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.03566631674766541</v>
+        <v>6.652260253758868e-07</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0009367037564516068</v>
+        <v>1.780259594852396e-06</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01508111786097288</v>
+        <v>1.45024387165904e-06</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.02673620730638504</v>
+        <v>1.375677129544783e-06</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.053232342004776</v>
+        <v>1.229059876095562e-07</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.02745743282139301</v>
+        <v>1.502063923908281e-06</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.03758683055639267</v>
+        <v>3.971777459810255e-06</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.03593746200203896</v>
+        <v>6.471414053521585e-06</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.008699956350028515</v>
+        <v>2.319537770745228e-06</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.04895360767841339</v>
+        <v>2.832776999639464e-06</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.01858333498239517</v>
+        <v>1.579314130140119e-06</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.01330682635307312</v>
+        <v>3.50971362195196e-07</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.03658690676093102</v>
+        <v>3.269525223004166e-06</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.04507096856832504</v>
+        <v>7.154142622312065e-06</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.0003548730164766312</v>
+        <v>1.729962036733923e-06</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.004801653791218996</v>
+        <v>3.934395067517471e-07</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.02285493351519108</v>
+        <v>5.04914123666822e-06</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.01067063864320517</v>
+        <v>3.266671910751029e-07</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.01296741422265768</v>
+        <v>1.072618942998815e-06</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.003369247075170279</v>
+        <v>1.24123857858649e-08</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.01424833387136459</v>
+        <v>3.194267605977075e-07</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.06348598748445511</v>
+        <v>3.013607738466817e-06</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.2057624310255051</v>
+        <v>1.10243126982823e-05</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.02076514810323715</v>
+        <v>2.087683469653712e-06</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.002704799175262451</v>
+        <v>3.93887148675276e-06</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.004208200611174107</v>
+        <v>8.616360673840973e-07</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.006189410574734211</v>
+        <v>1.387281827192055e-06</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.009086544625461102</v>
+        <v>1.269308285145598e-07</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.04113975912332535</v>
+        <v>2.242582240796764e-06</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.008731871843338013</v>
+        <v>1.97682561520196e-06</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.03368451818823814</v>
+        <v>4.13207908422919e-06</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.03340050205588341</v>
+        <v>4.191108018858358e-06</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.04861626774072647</v>
+        <v>1.828513518375985e-06</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.02210799232125282</v>
+        <v>1.115426812248188e-06</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.06244330108165741</v>
+        <v>1.031734245771077e-05</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.02273620292544365</v>
+        <v>2.458877133904025e-06</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.005773835349828005</v>
+        <v>1.776794533725479e-06</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.06980571150779724</v>
+        <v>2.186990968766622e-06</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.01068164128810167</v>
+        <v>6.703271537844557e-07</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.002003493485972285</v>
+        <v>2.020751935560838e-06</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.07583297044038773</v>
+        <v>1.943137931448291e-06</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.005376845132559538</v>
+        <v>8.993116580313654e-07</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.08337651193141937</v>
+        <v>5.094238417768793e-07</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.08480727672576904</v>
+        <v>1.215809675159107e-06</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.02997677400708199</v>
+        <v>1.308035280089825e-06</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.009481950663030148</v>
+        <v>1.474686996516539e-06</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.04111015051603317</v>
+        <v>1.492641104050563e-07</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.0008143825689330697</v>
+        <v>9.500818691776658e-07</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.02690517716109753</v>
+        <v>5.126060841575963e-06</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.1201792657375336</v>
+        <v>1.009753214020748e-05</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.03442852571606636</v>
+        <v>1.843352038122248e-06</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.01820023730397224</v>
+        <v>3.859720436594216e-06</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.008517161011695862</v>
+        <v>1.01682326203445e-06</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.01477793790400028</v>
+        <v>6.181569460750325e-07</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.06127692013978958</v>
+        <v>1.265375317416328e-06</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.02649201080203056</v>
+        <v>3.615622290453757e-06</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.01301530189812183</v>
+        <v>1.930775823666409e-07</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.00338249932974577</v>
+        <v>9.576676802680595e-07</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.04338572546839714</v>
+        <v>2.532712414904381e-06</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.01031235139816999</v>
+        <v>5.405115075518552e-07</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.03039451688528061</v>
+        <v>1.099471660381823e-06</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.006077778991311789</v>
+        <v>9.743598639033735e-07</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.01533273793756962</v>
+        <v>2.285878508700989e-08</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.00365657452493906</v>
+        <v>1.349893068436359e-07</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.005694622173905373</v>
+        <v>9.848624813457718e-07</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.01954203844070435</v>
+        <v>1.008253207146481e-06</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.08753897994756699</v>
+        <v>2.340996843486209e-06</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.08241253346204758</v>
+        <v>5.780537321697921e-06</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.007178700529038906</v>
+        <v>1.307671482209116e-08</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.03111780621111393</v>
+        <v>3.340551756991772e-06</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.1016966477036476</v>
+        <v>1.063551098923199e-05</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.004699568264186382</v>
+        <v>1.270379470952321e-06</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.02040353789925575</v>
+        <v>2.773686901491601e-06</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.002151478081941605</v>
+        <v>4.205789082334377e-06</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.004277163185179234</v>
+        <v>4.247310698701767e-07</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.005529125221073627</v>
+        <v>3.810469024756458e-07</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.03490717336535454</v>
+        <v>2.18126479012426e-06</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.0162227600812912</v>
+        <v>8.853024269228627e-08</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.04575489088892937</v>
+        <v>1.345051941825659e-06</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.0007011388661339879</v>
+        <v>9.957623205991695e-07</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.01672201603651047</v>
+        <v>4.188279092431912e-07</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.005328604485839605</v>
+        <v>5.222015033723437e-07</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.007203264161944389</v>
+        <v>1.432139242751873e-06</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.01374348532408476</v>
+        <v>9.085892429538944e-07</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.07145756483078003</v>
+        <v>6.018381100147963e-07</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.133560985326767</v>
+        <v>1.280673018300149e-06</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.0128092784434557</v>
+        <v>1.267958680273296e-07</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.1014334708452225</v>
+        <v>4.147417485000915e-07</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.05176009610295296</v>
+        <v>2.225501020802767e-06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.01861606165766716</v>
+        <v>2.816489768520114e-06</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.101417638361454</v>
+        <v>1.683412392594619e-06</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.02761193178594112</v>
+        <v>1.442201380541519e-07</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.01664618216454983</v>
+        <v>7.715502761129756e-06</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.03645668923854828</v>
+        <v>3.967933480453212e-06</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.04481464996933937</v>
+        <v>2.505075599401607e-06</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.009931276552379131</v>
+        <v>1.177970602839196e-06</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.004545066505670547</v>
+        <v>2.684406013031548e-07</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.04897624626755714</v>
+        <v>5.577037143211783e-08</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.001173430471681058</v>
+        <v>1.156714461103547e-06</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.02600969187915325</v>
+        <v>1.942182962011429e-06</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.02460051327943802</v>
+        <v>3.687935645757534e-07</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.01701196096837521</v>
+        <v>2.005167232255189e-07</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.01338613033294678</v>
+        <v>1.575247210894304e-06</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.01347362343221903</v>
+        <v>2.903557287936565e-06</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.01414648722857237</v>
+        <v>1.187664452118042e-06</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.05256993323564529</v>
+        <v>1.587019596627215e-06</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.02857338078320026</v>
+        <v>2.139016032742802e-06</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.01140087191015482</v>
+        <v>6.450533760471444e-07</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.03124927543103695</v>
+        <v>5.78173739995691e-07</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.01257406920194626</v>
+        <v>3.548046151991002e-06</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.01162736117839813</v>
+        <v>3.52828266159122e-07</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.02560309320688248</v>
+        <v>1.810676394597976e-06</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.0007781597669236362</v>
+        <v>6.782422588003101e-07</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.003857630072161555</v>
+        <v>1.452031597182213e-06</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.06855486333370209</v>
+        <v>3.538688361004461e-06</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.02289576269686222</v>
+        <v>6.234914735614439e-07</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.01890003308653831</v>
+        <v>1.853906269388972e-06</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.01688153855502605</v>
+        <v>8.687218269187724e-07</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.01185865420848131</v>
+        <v>2.669816865363828e-07</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.006468367762863636</v>
+        <v>2.78942479781108e-07</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.03793904930353165</v>
+        <v>1.085625513042032e-06</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.01144996099174023</v>
+        <v>1.399313077854458e-06</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.03970495611429214</v>
+        <v>2.997210231114877e-06</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.03006858378648758</v>
+        <v>1.218954821524676e-07</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.004170283209532499</v>
+        <v>8.369829060939082e-07</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.03649134933948517</v>
+        <v>5.291959723763284e-07</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.01556682679802179</v>
+        <v>1.824432729335967e-07</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.02158186957240105</v>
+        <v>1.107300704461522e-06</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.01229071896523237</v>
+        <v>6.350526291498682e-07</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.00375857762992382</v>
+        <v>1.022314222609566e-06</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.03118126653134823</v>
+        <v>2.745958454397623e-06</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.009189816191792488</v>
+        <v>1.527238850940194e-07</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.0344826728105545</v>
+        <v>9.404271850144141e-07</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0003795376978814602</v>
+        <v>6.196205504238605e-07</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.01624134182929993</v>
+        <v>5.403325076258625e-08</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.008871715515851974</v>
+        <v>1.212799816130428e-08</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.008033097721636295</v>
+        <v>1.648796342124115e-06</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.01743160933256149</v>
+        <v>1.498129790888925e-06</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.02718186937272549</v>
+        <v>9.764562491909601e-07</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.03809515386819839</v>
+        <v>8.766191967879422e-07</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.02770721539855003</v>
+        <v>1.324735876551131e-06</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.01535483542829752</v>
+        <v>1.146108616012498e-06</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.000884148757904768</v>
+        <v>1.425123173248721e-06</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.009796134196221828</v>
+        <v>1.049530624186445e-06</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.009105653502047062</v>
+        <v>4.065084624471638e-08</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.009984896518290043</v>
+        <v>2.146564156646491e-06</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.003778975922614336</v>
+        <v>3.628342710726429e-06</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.006880262866616249</v>
+        <v>2.435212309137569e-06</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.006040327250957489</v>
+        <v>5.304049409460276e-06</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.04043694213032722</v>
+        <v>5.474973477248568e-06</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.06209131330251694</v>
+        <v>3.524718067637878e-06</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.06754597276449203</v>
+        <v>6.448818112403387e-06</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.01636102981865406</v>
+        <v>8.788435934548033e-08</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.01468458585441113</v>
+        <v>1.007780269901559e-06</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.05505209416151047</v>
+        <v>2.733764176809927e-06</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.003878105897456408</v>
+        <v>1.465229388486478e-06</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.02851093746721745</v>
+        <v>3.697235570143675e-06</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.06269833445549011</v>
+        <v>3.601927801355487e-06</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.01900376006960869</v>
+        <v>1.55738393914362e-06</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.04002806171774864</v>
+        <v>2.375438953094999e-06</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.01160092186182737</v>
+        <v>2.310824584128568e-06</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.02670126967132092</v>
+        <v>9.193583139222028e-08</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.06597878783941269</v>
+        <v>6.089923090257798e-07</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.05632986128330231</v>
+        <v>1.98625684788567e-06</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.006385993212461472</v>
+        <v>2.795741238514893e-08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.08506237715482712</v>
+        <v>0.06281998753547668</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2788068652153015</v>
+        <v>0.1182707846164703</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0003999681212007999</v>
+        <v>0.05129249393939972</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02118871361017227</v>
+        <v>0.002278157509863377</v>
       </c>
       <c r="E11" t="n">
-        <v>0.141328752040863</v>
+        <v>0.0472697913646698</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0574692003428936</v>
+        <v>0.02327997609972954</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01489623822271824</v>
+        <v>0.01399309560656548</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01433665677905083</v>
+        <v>0.01086356211453676</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04185043275356293</v>
+        <v>0.02907415106892586</v>
       </c>
       <c r="J11" t="n">
-        <v>0.06744799017906189</v>
+        <v>0.03669215366244316</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2173706889152527</v>
+        <v>0.1721829771995544</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01442959904670715</v>
+        <v>0.04182596132159233</v>
       </c>
       <c r="M11" t="n">
-        <v>0.08937110006809235</v>
+        <v>0.02596709690988064</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2295583039522171</v>
+        <v>0.04877177998423576</v>
       </c>
       <c r="O11" t="n">
-        <v>0.09533977508544922</v>
+        <v>0.005102363880723715</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0510902926325798</v>
+        <v>0.001214350108057261</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1293697208166122</v>
+        <v>0.02185324393212795</v>
       </c>
       <c r="R11" t="n">
-        <v>0.08354569971561432</v>
+        <v>0.03301337733864784</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0131248002871871</v>
+        <v>0.001770810689777136</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1184171512722969</v>
+        <v>0.01914693787693977</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0266905277967453</v>
+        <v>0.01542392000555992</v>
       </c>
       <c r="V11" t="n">
-        <v>0.008321585133671761</v>
+        <v>0.02378233149647713</v>
       </c>
       <c r="W11" t="n">
-        <v>0.06158129498362541</v>
+        <v>0.01211692113429308</v>
       </c>
       <c r="X11" t="n">
-        <v>0.06081823632121086</v>
+        <v>0.01203536614775658</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.04302923381328583</v>
+        <v>0.0008431635797023773</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.005670459475368261</v>
+        <v>0.009035838767886162</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.02643659338355064</v>
+        <v>0.02265341393649578</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01833861880004406</v>
+        <v>0.02168766781687737</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.05955542251467705</v>
+        <v>0.0001706331968307495</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.02998072095215321</v>
+        <v>0.03603967279195786</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0711812749505043</v>
+        <v>0.02411610633134842</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.02717329189181328</v>
+        <v>0.01948439329862595</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.07966840267181396</v>
+        <v>0.01980583369731903</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.07894147932529449</v>
+        <v>0.005320891737937927</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.01583311334252357</v>
+        <v>0.02691679075360298</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.005389829631894827</v>
+        <v>0.008474946953356266</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.04906302690505981</v>
+        <v>0.001799875288270414</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.07321862876415253</v>
+        <v>0.05955393984913826</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.01071078050881624</v>
+        <v>0.00416900310665369</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.01424527727067471</v>
+        <v>0.01032390166074038</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.008277026936411858</v>
+        <v>0.02529411949217319</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.05912512540817261</v>
+        <v>0.01127025205641985</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.03342018276453018</v>
+        <v>0.00548191461712122</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.02109255641698837</v>
+        <v>0.01657224632799625</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.01474021468311548</v>
+        <v>0.003672086633741856</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.09716188162565231</v>
+        <v>0.005959450732916594</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.238751158118248</v>
+        <v>0.1264374852180481</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.009115812368690968</v>
+        <v>0.01669211126863956</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.03405208885669708</v>
+        <v>0.01271511428058147</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.07626973837614059</v>
+        <v>0.01852626353502274</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.03166001662611961</v>
+        <v>0.00751065369695425</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.002313812728971243</v>
+        <v>0.006184994243085384</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.04502216354012489</v>
+        <v>0.007295283954590559</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.03362705186009407</v>
+        <v>0.0001190596958622336</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.0459941104054451</v>
+        <v>0.06487121433019638</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.0007700370624661446</v>
+        <v>0.03510482609272003</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.02362700924277306</v>
+        <v>0.0478350967168808</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.02234708704054356</v>
+        <v>0.003343179821968079</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.1694160997867584</v>
+        <v>0.0685470774769783</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.01528600696474314</v>
+        <v>0.007298590615391731</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.01787713728845119</v>
+        <v>0.003771367482841015</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.08026514202356339</v>
+        <v>0.008027896285057068</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.07999113947153091</v>
+        <v>0.02366935275495052</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.009084186516702175</v>
+        <v>0.008412491530179977</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.05146852135658264</v>
+        <v>0.01028070971369743</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.01206152513623238</v>
+        <v>0.001425422495231032</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.1155291125178337</v>
+        <v>0.01675322651863098</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.1449514776468277</v>
+        <v>0.01288264431059361</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.03887277096509933</v>
+        <v>0.01062959246337414</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.007505254354327917</v>
+        <v>0.03569743782281876</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.05927648395299911</v>
+        <v>0.001688067801296711</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.04614327102899551</v>
+        <v>0.00736139202490449</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.04509801417589188</v>
+        <v>0.01516346819698811</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.143721267580986</v>
+        <v>0.09327153861522675</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.02252429351210594</v>
+        <v>0.01376113761216402</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.02376314252614975</v>
+        <v>0.02673757448792458</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.009575606323778629</v>
+        <v>0.005120592191815376</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.01614979468286037</v>
+        <v>0.005690434947609901</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.05079926550388336</v>
+        <v>0.01943809539079666</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.02539068274199963</v>
+        <v>0.006578756030648947</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.02160735800862312</v>
+        <v>0.01508890185505152</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.005258594639599323</v>
+        <v>0.01086073089390993</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.05178347229957581</v>
+        <v>0.0489535927772522</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.01229823473840952</v>
+        <v>0.0168189276009798</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.04391699284315109</v>
+        <v>0.01194735616445541</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.006251523271203041</v>
+        <v>0.003485341323539615</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.004375619813799858</v>
+        <v>0.01035001594573259</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.004945486783981323</v>
+        <v>0.003772924188524485</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.001633840380236506</v>
+        <v>0.0006663023959845304</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.0005095308879390359</v>
+        <v>0.002729052444919944</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.115619383752346</v>
+        <v>0.01389019284397364</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.05692331865429878</v>
+        <v>0.07835560292005539</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.007359130308032036</v>
+        <v>0.01351747754961252</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.01673015579581261</v>
+        <v>0.01883591711521149</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.1155999824404716</v>
+        <v>0.03581945970654488</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.009946292266249657</v>
+        <v>0.007748187519609928</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.03149040043354034</v>
+        <v>0.01514184288680553</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.01827809400856495</v>
+        <v>0.01668164320290089</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.02223391644656658</v>
+        <v>0.00197636941447854</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.0006520426832139492</v>
+        <v>0.004503056406974792</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.05462896451354027</v>
+        <v>0.04759276658296585</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.01199101470410824</v>
+        <v>0.01583706215023994</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.05240657180547714</v>
+        <v>0.0007443712092936039</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.01310743298381567</v>
+        <v>0.003348277881741524</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.01620187051594257</v>
+        <v>0.007751167751848698</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.01746787875890732</v>
+        <v>0.0005240303580649197</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.009660975076258183</v>
+        <v>6.987608503550291e-05</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.004258428234606981</v>
+        <v>0.007073845714330673</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.1104670017957687</v>
+        <v>0.0007671101484447718</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.2301334738731384</v>
+        <v>0.06609456241130829</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.02296676300466061</v>
+        <v>0.02685553207993507</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.03285281360149384</v>
+        <v>0.01379482448101044</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.01870989426970482</v>
+        <v>0.01027432642877102</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.08538346737623215</v>
+        <v>0.03859858214855194</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.06370014697313309</v>
+        <v>0.001267487881705165</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.05261318758130074</v>
+        <v>0.01816756278276443</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.04805903509259224</v>
+        <v>0.006977051496505737</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.04993688687682152</v>
+        <v>0.001882895361632109</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.08566196262836456</v>
+        <v>0.01642907969653606</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.01398214790970087</v>
+        <v>0.01114955358207226</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.04327793419361115</v>
+        <v>0.01203313656151295</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.05042344704270363</v>
+        <v>0.005951644387096167</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.001658761873841286</v>
+        <v>0.02431475184857845</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.01683354005217552</v>
+        <v>0.003915007226169109</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.001252594869583845</v>
+        <v>0.01592760346829891</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.03450635820627213</v>
+        <v>0.01344786956906319</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.01865248382091522</v>
+        <v>0.02905565872788429</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.04218669608235359</v>
+        <v>0.05739198625087738</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.05023962631821632</v>
+        <v>0.02165620401501656</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.0675930380821228</v>
+        <v>0.003879933152347803</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.05105780065059662</v>
+        <v>0.01139700412750244</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.00881048571318388</v>
+        <v>0.02879374660551548</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.04150090739130974</v>
+        <v>0.005527826026082039</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.01567673124372959</v>
+        <v>0.02927924692630768</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.03091116063296795</v>
+        <v>0.01607495918869972</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.03025669045746326</v>
+        <v>0.006886286195367575</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.05613048002123833</v>
+        <v>0.01525549590587616</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.01141259726136923</v>
+        <v>0.001008818857371807</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.07022891938686371</v>
+        <v>0.007391518913209438</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.02504252828657627</v>
+        <v>0.007291818968951702</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.0375843308866024</v>
+        <v>0.01577873155474663</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.01978687755763531</v>
+        <v>3.373576328158379e-05</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.01750272512435913</v>
+        <v>0.004597801715135574</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.01501315273344517</v>
+        <v>0.005117344669997692</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.02335390262305737</v>
+        <v>0.0002838065847754478</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.01285847462713718</v>
+        <v>0.02753720991313457</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.01921033300459385</v>
+        <v>0.001691619167104363</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.01946999877691269</v>
+        <v>0.01127651147544384</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.00533123966306448</v>
+        <v>0.005136642139405012</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.01273093372583389</v>
+        <v>0.0027079819701612</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.01233520824462175</v>
+        <v>0.002299664309248328</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.02323878929018974</v>
+        <v>0.006866832263767719</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.01046169549226761</v>
+        <v>0.004251467529684305</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.008360456675291061</v>
+        <v>0.007887887768447399</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.04505056142807007</v>
+        <v>0.05536423251032829</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.00783046055585146</v>
+        <v>0.01767397299408913</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.04735565558075905</v>
+        <v>0.006038918625563383</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.003509512636810541</v>
+        <v>0.004096966236829758</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.009359585121273994</v>
+        <v>0.00790566299110651</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.01207984704524279</v>
+        <v>0.003846813458949327</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.01141123101115227</v>
+        <v>0.001700794091448188</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.004160020966082811</v>
+        <v>0.008032888174057007</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.0633050873875618</v>
+        <v>0.01090228091925383</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.0431085042655468</v>
+        <v>0.01170921418815851</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.03443057835102081</v>
+        <v>0.02684719115495682</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.03331043571233749</v>
+        <v>0.02070729434490204</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.02085584402084351</v>
+        <v>0.01547909900546074</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.007712480612099171</v>
+        <v>0.01158583723008633</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.03311508893966675</v>
+        <v>0.01070960517972708</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.001299686264246702</v>
+        <v>0.001722212182357907</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.003377060405910015</v>
+        <v>0.01980218663811684</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.04821013659238815</v>
+        <v>0.0144392242655158</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.05353661626577377</v>
+        <v>0.01502616610378027</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.03413455933332443</v>
+        <v>0.004495781846344471</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.1323608458042145</v>
+        <v>0.001424104906618595</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.07059346139431</v>
+        <v>0.08349324017763138</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.04249294474720955</v>
+        <v>0.026504872366786</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.0008980371057987213</v>
+        <v>0.01017948146909475</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.03325396031141281</v>
+        <v>0.02562100253999233</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.01786896213889122</v>
+        <v>0.03146369755268097</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.03180381655693054</v>
+        <v>0.008510662242770195</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.06660138070583344</v>
+        <v>0.03390638902783394</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.02160818874835968</v>
+        <v>0.01144576258957386</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.1009142026305199</v>
+        <v>0.001065222779288888</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.1396520733833313</v>
+        <v>0.009480835869908333</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.03781072422862053</v>
+        <v>0.001730387797579169</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.1005512699484825</v>
+        <v>0.008591760881245136</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.1064713671803474</v>
+        <v>0.02480717562139034</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.02106037735939026</v>
+        <v>0.01386512070894241</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.02088192477822304</v>
+        <v>0.02658545970916748</v>
       </c>
       <c r="B12" t="n">
-        <v>0.09047577530145645</v>
+        <v>0.06995849311351776</v>
       </c>
       <c r="C12" t="n">
-        <v>0.01341110095381737</v>
+        <v>0.01614433340728283</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01862579956650734</v>
+        <v>0.02265710942447186</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05748897418379784</v>
+        <v>0.03967098891735077</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01469107624143362</v>
+        <v>0.01774190925061703</v>
       </c>
       <c r="G12" t="n">
-        <v>0.069874607026577</v>
+        <v>0.02870738506317139</v>
       </c>
       <c r="H12" t="n">
-        <v>0.008804119192063808</v>
+        <v>0.0365200974047184</v>
       </c>
       <c r="I12" t="n">
-        <v>0.004536574706435204</v>
+        <v>0.02600279822945595</v>
       </c>
       <c r="J12" t="n">
-        <v>0.02710543572902679</v>
+        <v>0.02265087887644768</v>
       </c>
       <c r="K12" t="n">
-        <v>0.06303507089614868</v>
+        <v>0.09458907693624496</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003777291625738144</v>
+        <v>0.003775808960199356</v>
       </c>
       <c r="M12" t="n">
-        <v>0.03530294820666313</v>
+        <v>0.02445556968450546</v>
       </c>
       <c r="N12" t="n">
-        <v>0.05832254514098167</v>
+        <v>0.03017359226942062</v>
       </c>
       <c r="O12" t="n">
-        <v>0.02151091024279594</v>
+        <v>0.02474223449826241</v>
       </c>
       <c r="P12" t="n">
-        <v>0.05256634950637817</v>
+        <v>0.04283526167273521</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.008642380125820637</v>
+        <v>0.03872596099972725</v>
       </c>
       <c r="R12" t="n">
-        <v>0.01022624038159847</v>
+        <v>0.003714060876518488</v>
       </c>
       <c r="S12" t="n">
-        <v>0.009954757988452911</v>
+        <v>0.01054354012012482</v>
       </c>
       <c r="T12" t="n">
-        <v>0.03816474229097366</v>
+        <v>0.004460491240024567</v>
       </c>
       <c r="U12" t="n">
-        <v>0.008320792578160763</v>
+        <v>0.008858714252710342</v>
       </c>
       <c r="V12" t="n">
-        <v>0.02603249065577984</v>
+        <v>0.001740842591971159</v>
       </c>
       <c r="W12" t="n">
-        <v>0.04577572643756866</v>
+        <v>0.003711761208251119</v>
       </c>
       <c r="X12" t="n">
-        <v>0.02220502123236656</v>
+        <v>0.01256870850920677</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.005492898635566235</v>
+        <v>0.008908780291676521</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.01159390341490507</v>
+        <v>0.007175591308623552</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.001068546785973012</v>
+        <v>0.00238012382760644</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.01761072874069214</v>
+        <v>0.02135762758553028</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.03154692798852921</v>
+        <v>0.009566040709614754</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.01862885616719723</v>
+        <v>0.03288592025637627</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.008272770792245865</v>
+        <v>0.002811122685670853</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.00476563349366188</v>
+        <v>0.02523119561374187</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.01062980480492115</v>
+        <v>0.006194331217557192</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.001832899637520313</v>
+        <v>0.003384246956557035</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.006326935719698668</v>
+        <v>0.004227543249726295</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.002504585543647408</v>
+        <v>0.005774963181465864</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.02383662760257721</v>
+        <v>0.01075570750981569</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.005678827408701181</v>
+        <v>0.03976735472679138</v>
       </c>
       <c r="AM12" t="n">
-        <v>8.781343785813078e-05</v>
+        <v>0.001624519005417824</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.01653530076146126</v>
+        <v>0.003377262502908707</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.005626085679978132</v>
+        <v>0.01917261257767677</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.001464389264583588</v>
+        <v>0.01062102150171995</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.01106325723230839</v>
+        <v>0.00490340031683445</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.01440446265041828</v>
+        <v>0.004157526418566704</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.00128441583365202</v>
+        <v>0.010396808385849</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.01911867782473564</v>
+        <v>0.01674230769276619</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.08161481469869614</v>
+        <v>0.0810486227273941</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.003900028299540281</v>
+        <v>0.01644750870764256</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.03286490589380264</v>
+        <v>0.00950484536588192</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.00142214703373611</v>
+        <v>0.007592256646603346</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.02620528824627399</v>
+        <v>0.01744922250509262</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.02647934481501579</v>
+        <v>0.00356745021417737</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.005942433141171932</v>
+        <v>0.01766379363834858</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.0008389679715037346</v>
+        <v>0.007128365337848663</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.006752664688974619</v>
+        <v>0.01390606537461281</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.02410233207046986</v>
+        <v>0.04089128226041794</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.0262303464114666</v>
+        <v>0.004714411683380604</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.008033008314669132</v>
+        <v>0.004930032882839441</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.03062531538307667</v>
+        <v>0.04021425917744637</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.01008007768541574</v>
+        <v>0.009094354696571827</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.02883892878890038</v>
+        <v>0.01193718705326319</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.002461113734170794</v>
+        <v>0.02509011514484882</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.01063383277505636</v>
+        <v>0.02112941816449165</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.004556963220238686</v>
+        <v>0.01133042946457863</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.02266959473490715</v>
+        <v>0.01447300985455513</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.01558845769613981</v>
+        <v>0.007415586616843939</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.02762085385620594</v>
+        <v>0.01733815670013428</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.05253835767507553</v>
+        <v>0.01514238491654396</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.002753861714154482</v>
+        <v>0.01684376411139965</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.004809393547475338</v>
+        <v>0.01434530317783356</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.02264304645359516</v>
+        <v>0.004477883689105511</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.002764417557045817</v>
+        <v>0.01251558493822813</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.0006171143613755703</v>
+        <v>0.01498926617205143</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.02791095152497292</v>
+        <v>0.05707473680377007</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.02242160774767399</v>
+        <v>0.007261861115694046</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.02882947772741318</v>
+        <v>0.01246894896030426</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.002796436659991741</v>
+        <v>0.002397303003817797</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.006431860383599997</v>
+        <v>0.005733651109039783</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.008230037987232208</v>
+        <v>0.001722846180200577</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.02227120660245419</v>
+        <v>0.01196838729083538</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.006405491847544909</v>
+        <v>0.006395302247256041</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.005219951272010803</v>
+        <v>0.007782279513776302</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.02162534929811954</v>
+        <v>0.02461067773401737</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.005334081593900919</v>
+        <v>0.0004397090524435043</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.002088358858600259</v>
+        <v>0.008766960352659225</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.007256480399519205</v>
+        <v>0.004329164978116751</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.0008392580784857273</v>
+        <v>0.009073825553059578</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.009096377529203892</v>
+        <v>0.003294988535344601</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.004454659298062325</v>
+        <v>0.006389843299984932</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.0005639874725602567</v>
+        <v>0.01189502328634262</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.03735030069947243</v>
+        <v>0.01088855415582657</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.03425700962543488</v>
+        <v>0.03373262286186218</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.002637375146150589</v>
+        <v>0.01606034487485886</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.008780425414443016</v>
+        <v>0.006283524446189404</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.04007092118263245</v>
+        <v>1.434027217328548e-05</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.003210503375157714</v>
+        <v>0.003900961019098759</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.01668582111597061</v>
+        <v>0.02365162596106529</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.01244898699223995</v>
+        <v>0.01175935287028551</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.01844639703631401</v>
+        <v>0.01087845861911774</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.008238024078309536</v>
+        <v>0.005976413376629353</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.0159981045871973</v>
+        <v>0.02593705989420414</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.008547006174921989</v>
+        <v>0.001268258318305016</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.008412135764956474</v>
+        <v>0.005724058486521244</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.002931049559265375</v>
+        <v>0.006630813702940941</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.0004826211370527744</v>
+        <v>0.009000105783343315</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.01025489438325167</v>
+        <v>0.005092187318950891</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.005837067030370235</v>
+        <v>0.007519899401813745</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.001053965534083545</v>
+        <v>0.01314247585833073</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.0007825698703527451</v>
+        <v>0.01084617711603642</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.04245304688811302</v>
+        <v>0.0190807580947876</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.01175149530172348</v>
+        <v>0.02619373984634876</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.0173015333712101</v>
+        <v>0.00774753000587225</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.01202128827571869</v>
+        <v>0.005945190787315369</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.02673391252756119</v>
+        <v>0.02617601864039898</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.001900935079902411</v>
+        <v>0.0114632248878479</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.009623272344470024</v>
+        <v>0.0117345480248332</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.02442997321486473</v>
+        <v>0.002104669809341431</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.003574877046048641</v>
+        <v>0.01079510152339935</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.01183512527495623</v>
+        <v>0.008483586832880974</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.01897091418504715</v>
+        <v>0.006514156702905893</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.01380022615194321</v>
+        <v>0.01986994594335556</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.0145316943526268</v>
+        <v>0.008091896772384644</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.01265798322856426</v>
+        <v>0.02351443283259869</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.004022690933197737</v>
+        <v>0.01297776494175196</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.01361858658492565</v>
+        <v>0.01242112461477518</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.0001515727490186691</v>
+        <v>0.02720149792730808</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.0001738346181809902</v>
+        <v>0.007365853060036898</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.02251410111784935</v>
+        <v>0.00816644448786974</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.01001035422086716</v>
+        <v>0.0019541229121387</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.004725150763988495</v>
+        <v>0.01246212795376778</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.01233054231852293</v>
+        <v>0.005067327059805393</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.01263777446001768</v>
+        <v>0.03474330902099609</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.006669607944786549</v>
+        <v>0.000584571564104408</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.009288463741540909</v>
+        <v>0.01099524553865194</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.01307373773306608</v>
+        <v>0.005912591703236103</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.01249849610030651</v>
+        <v>0.003443011082708836</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.001412560231983662</v>
+        <v>0.02799557521939278</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.001635901746340096</v>
+        <v>0.005971074104309082</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.02667517587542534</v>
+        <v>0.0008450266905128956</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.003653372870758176</v>
+        <v>0.006327345967292786</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.001739165280014277</v>
+        <v>0.001455529010854661</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.01203374937176704</v>
+        <v>0.004954679869115353</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.004486666992306709</v>
+        <v>0.003228073939681053</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.002332527423277497</v>
+        <v>0.008328459225594997</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.01693476364016533</v>
+        <v>0.01125677302479744</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.0004939356585964561</v>
+        <v>0.01571929082274437</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.01101904548704624</v>
+        <v>0.002714070491492748</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.006884408183395863</v>
+        <v>0.0197443775832653</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.0008447356522083282</v>
+        <v>0.005423962604254484</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.005829740781337023</v>
+        <v>0.002592107281088829</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.003337271511554718</v>
+        <v>0.005330620333552361</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.001753323362208903</v>
+        <v>0.01004782784730196</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.01075086556375027</v>
+        <v>0.0001127651194110513</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.009307452477514744</v>
+        <v>0.006221157964318991</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.0158841609954834</v>
+        <v>0.02713519521057606</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.003188122296705842</v>
+        <v>0.001823754981160164</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.003224780783057213</v>
+        <v>0.004622585140168667</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.004513473249971867</v>
+        <v>0.002061937004327774</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.003111609490588307</v>
+        <v>0.007280712481588125</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.008626289665699005</v>
+        <v>0.002058998448774219</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.00888434424996376</v>
+        <v>0.007705408614128828</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.0002072585775749758</v>
+        <v>0.01359599083662033</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.01223673392087221</v>
+        <v>0.01545856799930334</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.003589910920709372</v>
+        <v>0.01332639902830124</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.01453255955129862</v>
+        <v>0.02108092792332172</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.008569080382585526</v>
+        <v>0.009903549216687679</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.01382933929562569</v>
+        <v>0.01154235098510981</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.009789028204977512</v>
+        <v>0.01706342399120331</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.00105635670479387</v>
+        <v>0.004261122085154057</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.008589770644903183</v>
+        <v>0.01854259148240089</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.02376476116478443</v>
+        <v>0.04730546846985817</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.01655737496912479</v>
+        <v>0.01365851610898972</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.0213947631418705</v>
+        <v>0.04184349626302719</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.03030078485608101</v>
+        <v>0.03149236366152763</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.02641344256699085</v>
+        <v>0.02954141609370708</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.01553357485681772</v>
+        <v>0.01839150302112103</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.01714687049388885</v>
+        <v>0.03358402103185654</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.01090442016720772</v>
+        <v>0.01706042513251305</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.01746058464050293</v>
+        <v>0.02171428129076958</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.005094666033983231</v>
+        <v>0.008869290351867676</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.01770684495568275</v>
+        <v>0.008962236344814301</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.00846108328551054</v>
+        <v>0.02737042494118214</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.01032515801489353</v>
+        <v>0.02031398564577103</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.03383099660277367</v>
+        <v>0.007030773907899857</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.004467115737497807</v>
+        <v>0.0339978039264679</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.01783309504389763</v>
+        <v>0.005988902878016233</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.01368477940559387</v>
+        <v>0.004674283787608147</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.03397271037101746</v>
+        <v>0.01276080030947924</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.0028561782091856</v>
+        <v>0.0009619317715987563</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.00388949504122138</v>
+        <v>0.007943622767925262</v>
       </c>
       <c r="B13" t="n">
-        <v>0.05446913838386536</v>
+        <v>0.03927896171808243</v>
       </c>
       <c r="C13" t="n">
-        <v>0.007831327617168427</v>
+        <v>0.009705894626677036</v>
       </c>
       <c r="D13" t="n">
-        <v>0.009990934282541275</v>
+        <v>0.001698960899375379</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01750560663640499</v>
+        <v>0.02102447673678398</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01414038240909576</v>
+        <v>0.01878062263131142</v>
       </c>
       <c r="G13" t="n">
-        <v>0.00498467218130827</v>
+        <v>0.005377690773457289</v>
       </c>
       <c r="H13" t="n">
-        <v>0.006590543314814568</v>
+        <v>0.01167875621467829</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02603121660649776</v>
+        <v>0.009636319242417812</v>
       </c>
       <c r="J13" t="n">
-        <v>0.004780028015375137</v>
+        <v>0.003924802411347628</v>
       </c>
       <c r="K13" t="n">
-        <v>0.03686675056815147</v>
+        <v>0.05664125084877014</v>
       </c>
       <c r="L13" t="n">
-        <v>0.001900281524285674</v>
+        <v>0.004885880742222071</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01473830081522465</v>
+        <v>0.01429134048521519</v>
       </c>
       <c r="N13" t="n">
-        <v>0.01582867652177811</v>
+        <v>0.02565563470125198</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01142634358257055</v>
+        <v>0.01695589534938335</v>
       </c>
       <c r="P13" t="n">
-        <v>0.001586141530424356</v>
+        <v>0.004661335609853268</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0006942122709006071</v>
+        <v>0.007029812317341566</v>
       </c>
       <c r="R13" t="n">
-        <v>0.02581331878900528</v>
+        <v>0.005650331266224384</v>
       </c>
       <c r="S13" t="n">
-        <v>0.00172713934443891</v>
+        <v>0.002915656194090843</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01462545711547136</v>
+        <v>0.008021105080842972</v>
       </c>
       <c r="U13" t="n">
-        <v>0.004540675785392523</v>
+        <v>0.001928243087604642</v>
       </c>
       <c r="V13" t="n">
-        <v>4.953856114298105e-05</v>
+        <v>0.0173384677618742</v>
       </c>
       <c r="W13" t="n">
-        <v>0.001028200960718095</v>
+        <v>0.01094439066946507</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01170832570642233</v>
+        <v>0.006093556061387062</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.005348029546439648</v>
+        <v>0.0004643975989893079</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.004580465611070395</v>
+        <v>0.0002538818516768515</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.004999461118131876</v>
+        <v>0.008169686421751976</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.005176686681807041</v>
+        <v>0.003708013333380222</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.01292404625564814</v>
+        <v>0.00707470066845417</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.01046613045036793</v>
+        <v>0.01063051633536816</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.007973585277795792</v>
+        <v>0.0101226270198822</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0007214341312646866</v>
+        <v>0.01226690504699945</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.006215708795934916</v>
+        <v>0.007865096442401409</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.001931260921992362</v>
+        <v>0.001148832845501602</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.003995985724031925</v>
+        <v>0.01600184477865696</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.001290126703679562</v>
+        <v>0.0003265222767367959</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.007312658242881298</v>
+        <v>0.0006069325609132648</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.007557212840765715</v>
+        <v>0.02053203620016575</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.0006568922544829547</v>
+        <v>0.002668400993570685</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.001384257804602385</v>
+        <v>0.008377890102565289</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0006564349168911576</v>
+        <v>0.01437271665781736</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.004887244664132595</v>
+        <v>0.006433377973735332</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.001420750515535474</v>
+        <v>0.001316492795012891</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.001608508056961</v>
+        <v>0.007994177751243114</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.002010647673159838</v>
+        <v>0.002685071900486946</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.004009912721812725</v>
+        <v>0.008564346469938755</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.04316635802388191</v>
+        <v>0.06781154870986938</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.0008020830573514104</v>
+        <v>0.001759082777425647</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.002080354373902082</v>
+        <v>0.003546711057424545</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.003151002805680037</v>
+        <v>0.001233652816154063</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.003936144523322582</v>
+        <v>0.01057340390980244</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.008996070362627506</v>
+        <v>0.003727264469489455</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0008824255783110857</v>
+        <v>0.000439281779108569</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.00384054658934474</v>
+        <v>0.00152380159124732</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.00163949653506279</v>
+        <v>0.01856611669063568</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.008583244867622852</v>
+        <v>0.02336881309747696</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.006714630872011185</v>
+        <v>0.0153180118650198</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.002223988994956017</v>
+        <v>0.002028161659836769</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.01373155135661364</v>
+        <v>0.0269966796040535</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.01210483256727457</v>
+        <v>0.001012113760225475</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.007255099713802338</v>
+        <v>0.004799040034413338</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.002528483746573329</v>
+        <v>0.003150490112602711</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.01408283039927483</v>
+        <v>0.003239031415432692</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.00678835017606616</v>
+        <v>0.001887103775516152</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.004422247409820557</v>
+        <v>0.006288543809205294</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.0009512414690107107</v>
+        <v>0.001010374049656093</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.00110650691203773</v>
+        <v>0.01153104938566685</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.008295269683003426</v>
+        <v>0.01066325977444649</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.01176180131733418</v>
+        <v>0.003321313066408038</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.002190278144553304</v>
+        <v>0.0226428247988224</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.0004820627509616315</v>
+        <v>0.004545524250715971</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.002529080025851727</v>
+        <v>0.0049756970256567</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.0009385953890159726</v>
+        <v>0.01006564497947693</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.02420804090797901</v>
+        <v>0.04041203111410141</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.007716290187090635</v>
+        <v>0.001268929452635348</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.001056559616699815</v>
+        <v>0.01739243417978287</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.0009573280112817883</v>
+        <v>0.008537566289305687</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.01141155697405338</v>
+        <v>0.009797957725822926</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.0003270658198744059</v>
+        <v>0.005356556735932827</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.002974028000608087</v>
+        <v>0.001831103349104524</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.003406011965125799</v>
+        <v>0.008273521438241005</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.0004791696555912495</v>
+        <v>0.002810648642480373</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.009760532528162003</v>
+        <v>0.01823194697499275</v>
       </c>
       <c r="CF13" t="n">
-        <v>8.074901415966451e-05</v>
+        <v>0.004458551295101643</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.00285780755802989</v>
+        <v>0.0002843220718204975</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.0008524451404809952</v>
+        <v>0.003053504507988691</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.003548812586814165</v>
+        <v>0.004092835821211338</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.0007486386457458138</v>
+        <v>0.004103584215044975</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.0006123061175458133</v>
+        <v>0.0004194969078525901</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.005905551835894585</v>
+        <v>0.002158357296139002</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.01083861570805311</v>
+        <v>0.01527615636587143</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.01021759491413832</v>
+        <v>0.03519491478800774</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.001557191368192434</v>
+        <v>0.01498815603554249</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.002632639836519957</v>
+        <v>0.02126430161297321</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.01621312834322453</v>
+        <v>0.01072409190237522</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.001508196000941098</v>
+        <v>0.0007232489879243076</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.004995760507881641</v>
+        <v>0.006927622482180595</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.01021434366703033</v>
+        <v>0.001572820707224309</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.0004137752112001181</v>
+        <v>0.0006444784230552614</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.001228844397701323</v>
+        <v>0.005790921859443188</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.00841121468693018</v>
+        <v>0.01647631265223026</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.001595095149241388</v>
+        <v>0.004096333868801594</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.003350204322487116</v>
+        <v>0.002897261874750257</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.001217982266098261</v>
+        <v>0.001682106405496597</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.006010060664266348</v>
+        <v>0.003458159510046244</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0003178579499945045</v>
+        <v>0.002215273911133409</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.0001091597368940711</v>
+        <v>0.0007288248161785305</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.004272439982742071</v>
+        <v>0.003232858842238784</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.00226470734924078</v>
+        <v>0.01022088527679443</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.01970735378563404</v>
+        <v>0.005278336349874735</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.007375054992735386</v>
+        <v>0.004008498042821884</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.00532333180308342</v>
+        <v>0.009727532975375652</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.001104190363548696</v>
+        <v>0.001152197131887078</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0140651036053896</v>
+        <v>0.008981414139270782</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.008177166804671288</v>
+        <v>0.005537713877856731</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.008184239268302917</v>
+        <v>0.01252913754433393</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.002353630261495709</v>
+        <v>0.00160522572696209</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.00011385467951186</v>
+        <v>0.0005150813958607614</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.0007130546728149056</v>
+        <v>0.007800744846463203</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.001923687639646232</v>
+        <v>0.006519983522593975</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.002288258634507656</v>
+        <v>0.01168662682175636</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.005230715498328209</v>
+        <v>0.005182483699172735</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.006779780145734549</v>
+        <v>0.002821587026119232</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.002322059590369463</v>
+        <v>0.002183351665735245</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.002036627847701311</v>
+        <v>0.007419457659125328</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.004166124388575554</v>
+        <v>0.003342569340020418</v>
       </c>
       <c r="DW13" t="n">
-        <v>7.541291415691376e-05</v>
+        <v>0.005867005325853825</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.005297218449413776</v>
+        <v>0.01505009923130274</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.003952409140765667</v>
+        <v>0.01030283886939287</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.002940126694738865</v>
+        <v>0.002260294510051608</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.005762606859207153</v>
+        <v>0.008436528034508228</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.001823708415031433</v>
+        <v>0.01123126689344645</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.00409660954028368</v>
+        <v>0.0007888615364208817</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.005093760322779417</v>
+        <v>0.008076752535998821</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.004272664897143841</v>
+        <v>0.005535641219466925</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.002295807003974915</v>
+        <v>0.007490074262022972</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.003335716668516397</v>
+        <v>0.004262254573404789</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.000746320525649935</v>
+        <v>0.001737352227792144</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.001752416603267193</v>
+        <v>0.004156229551881552</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.001514891046099365</v>
+        <v>0.001624659635126591</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.003288301406428218</v>
+        <v>0.006607120390981436</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.004171366337686777</v>
+        <v>0.0008690572576597333</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.001742289634421468</v>
+        <v>0.001823836006224155</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.008319678716361523</v>
+        <v>0.001573781715705991</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.003306529019027948</v>
+        <v>0.001758382422849536</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.005233101546764374</v>
+        <v>0.0116402767598629</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.002559109358116984</v>
+        <v>0.004204011987894773</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.002554344013333321</v>
+        <v>0.005114790052175522</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.001525200204923749</v>
+        <v>0.0008182070450857282</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.01131982542574406</v>
+        <v>0.002387190004810691</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.001002727774903178</v>
+        <v>0.003269757144153118</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.001800132333301008</v>
+        <v>0.001716030994430184</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.0006005263421684504</v>
+        <v>0.004888202529400587</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.001517709577456117</v>
+        <v>0.003832414746284485</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.008816146291792393</v>
+        <v>0.0199145432561636</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.001683362410403788</v>
+        <v>0.005112946964800358</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.002811662619933486</v>
+        <v>0.001968055265024304</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.0001596082001924515</v>
+        <v>0.001531195244751871</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.005127612501382828</v>
+        <v>0.004899250343441963</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.0003912764950655401</v>
+        <v>0.004993542097508907</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.0008174838148988783</v>
+        <v>0.0008524954319000244</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.003280670382082462</v>
+        <v>0.003659091657027602</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.001196100376546383</v>
+        <v>0.00854786578565836</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.006393744610249996</v>
+        <v>0.008835947141051292</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.003436600556597114</v>
+        <v>0.004278007429093122</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.003538593417033553</v>
+        <v>0.01244621444493532</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.002946653170511127</v>
+        <v>0.009806415066123009</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.004830976482480764</v>
+        <v>0.002774088643491268</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.001531386631540954</v>
+        <v>0.003409742610529065</v>
       </c>
       <c r="FN13" t="n">
-        <v>9.440211579203606e-05</v>
+        <v>0.008338993415236473</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.003756976220756769</v>
+        <v>0.002843051217496395</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.001004367368295789</v>
+        <v>0.006429165136069059</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.017531618475914</v>
+        <v>0.01234579365700483</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.009393983520567417</v>
+        <v>0.00184820918366313</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.01121931150555611</v>
+        <v>0.0096783097833395</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.009298725053668022</v>
+        <v>0.01646727323532104</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.0003807061584666371</v>
+        <v>0.01296824589371681</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.004530768841505051</v>
+        <v>0.00178529426921159</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.0008149486966431141</v>
+        <v>0.0009090533712878823</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.002491933293640614</v>
+        <v>0.002330170245841146</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.005776767153292894</v>
+        <v>0.001725564594380558</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.007935477420687675</v>
+        <v>0.005363543517887592</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.006883746944367886</v>
+        <v>0.004104551859200001</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.0007201218977570534</v>
+        <v>0.003036893904209137</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.01281345076858997</v>
+        <v>0.00450194114819169</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.001826690859161317</v>
+        <v>0.004800808150321245</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.002566391136497259</v>
+        <v>0.005414429120719433</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.004246440716087818</v>
+        <v>0.007572091184556484</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.001370228594169021</v>
+        <v>0.004481606185436249</v>
       </c>
     </row>
     <row r="14">
@@ -8396,2278 +8396,2278 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.1179954558610916</v>
+        <v>0.4104501008987427</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7245736122131348</v>
+        <v>1.061859846115112</v>
       </c>
       <c r="C15" t="n">
-        <v>0.553650438785553</v>
+        <v>0.5748149752616882</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3561988770961761</v>
+        <v>0.4227858781814575</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5191683173179626</v>
+        <v>0.5424028635025024</v>
       </c>
       <c r="F15" t="n">
-        <v>0.06288135051727295</v>
+        <v>0.1592023223638535</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2216376960277557</v>
+        <v>0.3576422929763794</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1189236715435982</v>
+        <v>0.03080560080707073</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3326237499713898</v>
+        <v>0.1015903949737549</v>
       </c>
       <c r="J15" t="n">
-        <v>0.06247169896960258</v>
+        <v>0.149401992559433</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5239468216896057</v>
+        <v>1.322747707366943</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4392446875572205</v>
+        <v>0.5882056951522827</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3956593573093414</v>
+        <v>0.4377197027206421</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7366683483123779</v>
+        <v>0.5103361010551453</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2211258113384247</v>
+        <v>0.03239773958921432</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1870172172784805</v>
+        <v>0.2601810097694397</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.02742386050522327</v>
+        <v>0.1582449674606323</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2233647108078003</v>
+        <v>0.03161272406578064</v>
       </c>
       <c r="S15" t="n">
-        <v>0.01684434711933136</v>
+        <v>0.03051324747502804</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2011730968952179</v>
+        <v>0.2284597456455231</v>
       </c>
       <c r="U15" t="n">
-        <v>0.02322744578123093</v>
+        <v>0.02646487578749657</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1464105248451233</v>
+        <v>0.1621606349945068</v>
       </c>
       <c r="W15" t="n">
-        <v>0.02363389916718006</v>
+        <v>0.3571964204311371</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1499934643507004</v>
+        <v>0.1662062257528305</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.02618939429521561</v>
+        <v>0.06432781368494034</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.1118193939328194</v>
+        <v>0.04511492326855659</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.06919825822114944</v>
+        <v>0.1704706400632858</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.06374611705541611</v>
+        <v>0.03569405525922775</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1798637360334396</v>
+        <v>0.04030148684978485</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.06156739965081215</v>
+        <v>0.3511895835399628</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.0165023822337389</v>
+        <v>0.183934360742569</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.02586503885686398</v>
+        <v>0.2108361423015594</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.1318933814764023</v>
+        <v>0.2390371859073639</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.07290662825107574</v>
+        <v>0.1308639496564865</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.08569080382585526</v>
+        <v>0.3354421555995941</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.01489409990608692</v>
+        <v>0.1056733280420303</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.0673648938536644</v>
+        <v>0.1358109414577484</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.3548712730407715</v>
+        <v>0.5182480216026306</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.01495343819260597</v>
+        <v>0.02587299048900604</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.03189243003726006</v>
+        <v>0.008855033665895462</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.05294793844223022</v>
+        <v>0.491308331489563</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.1539498865604401</v>
+        <v>0.06289586424827576</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.02731499820947647</v>
+        <v>0.05157238617539406</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.07129107415676117</v>
+        <v>0.1129190102219582</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.1553135365247726</v>
+        <v>0.01476221159100533</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.2147783488035202</v>
+        <v>0.2687259912490845</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.7179211974143982</v>
+        <v>1.160094499588013</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.3531831502914429</v>
+        <v>0.02777481824159622</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.001853153109550476</v>
+        <v>0.2047367691993713</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.04277968406677246</v>
+        <v>0.0985942929983139</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.1068322062492371</v>
+        <v>0.2454101145267487</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.06497170776128769</v>
+        <v>0.09590134024620056</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.01692872308194637</v>
+        <v>0.2084936201572418</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.1501053869724274</v>
+        <v>0.06551223993301392</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.0338025689125061</v>
+        <v>0.4369876980781555</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.02584283053874969</v>
+        <v>0.372784435749054</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.1401838511228561</v>
+        <v>0.4834785461425781</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.2547204196453094</v>
+        <v>0.1848926395177841</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.5122390389442444</v>
+        <v>0.8582668900489807</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.07796400785446167</v>
+        <v>0.1568587571382523</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.1209135055541992</v>
+        <v>0.1186882331967354</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.05385633558034897</v>
+        <v>0.007068227976560593</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.1983236372470856</v>
+        <v>0.05705848708748817</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.2460772395133972</v>
+        <v>0.1481365710496902</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.1857943385839462</v>
+        <v>0.0164986252784729</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.1089174747467041</v>
+        <v>0.1950443536043167</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.03982216119766235</v>
+        <v>0.2118703424930573</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.3603243827819824</v>
+        <v>0.1334332227706909</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.1286254823207855</v>
+        <v>0.05264577642083168</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.1120667681097984</v>
+        <v>0.0009755082428455353</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.04887863621115685</v>
+        <v>0.1536343842744827</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.09852944314479828</v>
+        <v>0.09998159855604172</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.1719565093517303</v>
+        <v>0.1714813858270645</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.3764921128749847</v>
+        <v>0.9024970531463623</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.4152005910873413</v>
+        <v>0.007175995968282223</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.08579336851835251</v>
+        <v>0.2400162816047668</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.02295964770019054</v>
+        <v>0.2142226696014404</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.04557163640856743</v>
+        <v>0.1385584473609924</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.1320779025554657</v>
+        <v>0.2189015597105026</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.1219485998153687</v>
+        <v>0.009001513943076134</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.04694436490535736</v>
+        <v>0.04365148395299911</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.03328284621238708</v>
+        <v>0.2059604972600937</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.1376741975545883</v>
+        <v>0.4456079006195068</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.05498509109020233</v>
+        <v>0.1576651930809021</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.1362212747335434</v>
+        <v>0.2026520371437073</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.1255175769329071</v>
+        <v>0.08634825795888901</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.04230382665991783</v>
+        <v>0.02105671912431717</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.005295766517519951</v>
+        <v>0.01373858563601971</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.0441996231675148</v>
+        <v>0.08141535520553589</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.07614822685718536</v>
+        <v>0.02306880056858063</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.270976722240448</v>
+        <v>0.07828031480312347</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.03531821072101593</v>
+        <v>0.6388826966285706</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.06164440140128136</v>
+        <v>0.2817756831645966</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.1643382608890533</v>
+        <v>0.1180388256907463</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.1283021569252014</v>
+        <v>0.3606641292572021</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.1753357201814651</v>
+        <v>0.3163079023361206</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.03366709500551224</v>
+        <v>0.1374041885137558</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.04636888206005096</v>
+        <v>0.009263729676604271</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.01099900994449854</v>
+        <v>0.0478411465883255</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.04423800855875015</v>
+        <v>0.1353630423545837</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.07590427994728088</v>
+        <v>0.3856847584247589</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.04587899148464203</v>
+        <v>0.1506521105766296</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.1113647371530533</v>
+        <v>0.1253204941749573</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.1054073125123978</v>
+        <v>0.03348349034786224</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.0492975041270256</v>
+        <v>0.008853960782289505</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.01933104731142521</v>
+        <v>0.04190933331847191</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.03785388171672821</v>
+        <v>0.1228384152054787</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.1247885152697563</v>
+        <v>0.09931636601686478</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.04614972323179245</v>
+        <v>0.05488236248493195</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.2443691492080688</v>
+        <v>0.4853559732437134</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.08539529144763947</v>
+        <v>0.230604499578476</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.3199836909770966</v>
+        <v>0.2259616553783417</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.1472781300544739</v>
+        <v>0.1274784505367279</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.2431632578372955</v>
+        <v>0.2420213520526886</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.1027106940746307</v>
+        <v>0.1969036161899567</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.1403402537107468</v>
+        <v>0.1995418518781662</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.05799055472016335</v>
+        <v>0.2103606164455414</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.1307366937398911</v>
+        <v>0.2048127055168152</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.07498397678136826</v>
+        <v>0.1216268911957741</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.0618610717356205</v>
+        <v>0.2142880111932755</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.13697749376297</v>
+        <v>0.1701570749282837</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.01508177816867828</v>
+        <v>0.2869206070899963</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.1446404010057449</v>
+        <v>0.2445054948329926</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.02892143651843071</v>
+        <v>0.01831835322082043</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.01723858900368214</v>
+        <v>0.1890590190887451</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.1035550981760025</v>
+        <v>0.100453794002533</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.1687821894884109</v>
+        <v>0.2198543399572372</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.04525746405124664</v>
+        <v>0.5048233270645142</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.07951448112726212</v>
+        <v>0.2385998517274857</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.1576010584831238</v>
+        <v>0.1497534215450287</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.1331517249345779</v>
+        <v>0.2713960707187653</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.193540096282959</v>
+        <v>0.2009267508983612</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.0753248855471611</v>
+        <v>0.03482179343700409</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.02715791389346123</v>
+        <v>0.2446514219045639</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.04583602398633957</v>
+        <v>0.2254634350538254</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.01814066991209984</v>
+        <v>0.03841456025838852</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.03542168438434601</v>
+        <v>0.1949019730091095</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.01936440728604794</v>
+        <v>0.03408518806099892</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.1566064059734344</v>
+        <v>0.1098005920648575</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.1658390909433365</v>
+        <v>0.03145186603069305</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.09346780925989151</v>
+        <v>0.1094598025083542</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.1088596284389496</v>
+        <v>0.001747244969010353</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.05023240298032761</v>
+        <v>0.1601045578718185</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.1320904344320297</v>
+        <v>0.09344702214002609</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.04708041250705719</v>
+        <v>0.1062691956758499</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.05628045648336411</v>
+        <v>0.2811732888221741</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.1607698947191238</v>
+        <v>0.07788265496492386</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.02235675603151321</v>
+        <v>0.1407294422388077</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.1342644244432449</v>
+        <v>0.1424421072006226</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.1373536884784698</v>
+        <v>0.05388667806982994</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.1474252194166183</v>
+        <v>0.1318070590496063</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.1515420228242874</v>
+        <v>0.1054008454084396</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.2788904309272766</v>
+        <v>0.02974473871290684</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.03071307763457298</v>
+        <v>0.2072667181491852</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.07128638029098511</v>
+        <v>0.4549433290958405</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.03584695979952812</v>
+        <v>0.1697435975074768</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.1437828093767166</v>
+        <v>0.1488315463066101</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.147761270403862</v>
+        <v>0.04695970192551613</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.06312451511621475</v>
+        <v>0.01052744407206774</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.03151446208357811</v>
+        <v>0.008897760882973671</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.07119894772768021</v>
+        <v>0.1104532703757286</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.05735679715871811</v>
+        <v>0.09474809467792511</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.1659392416477203</v>
+        <v>0.006410926580429077</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.1794701963663101</v>
+        <v>0.05194594711065292</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.1564374268054962</v>
+        <v>0.3116388916969299</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.03395921736955643</v>
+        <v>0.1723979711532593</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.1198951601982117</v>
+        <v>0.3107992708683014</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.006635577417910099</v>
+        <v>0.07549547404050827</v>
       </c>
       <c r="FM15" t="n">
-        <v>0.1392398923635483</v>
+        <v>0.0626617968082428</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.02745651081204414</v>
+        <v>0.08119813352823257</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.1260387450456619</v>
+        <v>0.2059518396854401</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.07948105037212372</v>
+        <v>0.3904776275157928</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.00344080850481987</v>
+        <v>0.1763947606086731</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.2031301110982895</v>
+        <v>0.2089827358722687</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.361552894115448</v>
+        <v>0.04858313500881195</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.01047282852232456</v>
+        <v>0.4666222631931305</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.005451124161481857</v>
+        <v>0.01996804773807526</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.04898259788751602</v>
+        <v>0.1035658940672874</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.2228281050920486</v>
+        <v>0.0483526699244976</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.005837056785821915</v>
+        <v>0.2024384140968323</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.09214704483747482</v>
+        <v>0.2249674201011658</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.007820539176464081</v>
+        <v>0.3444029688835144</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.0949644148349762</v>
+        <v>0.1077128201723099</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.1034960299730301</v>
+        <v>0.02504914812743664</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.03884811326861382</v>
+        <v>0.01643076539039612</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.2256513386964798</v>
+        <v>0.01503872126340866</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.2172484397888184</v>
+        <v>0.08130833506584167</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.2849958837032318</v>
+        <v>0.01258939597755671</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.02438386157155037</v>
+        <v>0.10590860247612</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.0004423977225087583</v>
+        <v>0.0002450106258038431</v>
       </c>
       <c r="B16" t="n">
-        <v>0.002720593474805355</v>
+        <v>0.003236538032069802</v>
       </c>
       <c r="C16" t="n">
-        <v>0.001103228190913796</v>
+        <v>0.000357689248630777</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0008038835367187858</v>
+        <v>0.0004723120655398816</v>
       </c>
       <c r="E16" t="n">
-        <v>1.234703086083755e-05</v>
+        <v>0.001673977938480675</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0001681346038822085</v>
+        <v>0.0003979566099587828</v>
       </c>
       <c r="G16" t="n">
-        <v>5.426781717687845e-05</v>
+        <v>0.0002024792192969471</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0005826178239658475</v>
+        <v>0.0003884868929162621</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0007358287693932652</v>
+        <v>0.0003733296762220562</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0004009778203908354</v>
+        <v>0.0002569836215116084</v>
       </c>
       <c r="K16" t="n">
-        <v>0.002035234123468399</v>
+        <v>0.004267968237400055</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0006773346103727818</v>
+        <v>0.0002998971031047404</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0008397717028856277</v>
+        <v>0.001112241763621569</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0004919846542179585</v>
+        <v>0.002032986609265208</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0002769131679087877</v>
+        <v>0.0004141596728004515</v>
       </c>
       <c r="P16" t="n">
-        <v>5.04566851304844e-05</v>
+        <v>0.0002244926581624895</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0001091496451408602</v>
+        <v>0.0003274741466157138</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0004270084027666599</v>
+        <v>0.0004623923450708389</v>
       </c>
       <c r="S16" t="n">
-        <v>4.670709131460171e-06</v>
+        <v>0.0001197524543385953</v>
       </c>
       <c r="T16" t="n">
-        <v>0.000413580855820328</v>
+        <v>0.0004382458864711225</v>
       </c>
       <c r="U16" t="n">
-        <v>0.000163715667440556</v>
+        <v>0.0003314686473459005</v>
       </c>
       <c r="V16" t="n">
-        <v>2.568276249803603e-05</v>
+        <v>0.0004832345293834805</v>
       </c>
       <c r="W16" t="n">
-        <v>2.474414941389114e-05</v>
+        <v>0.0003029127838090062</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0009112699190154672</v>
+        <v>3.366316741448827e-05</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.0001216631280840375</v>
+        <v>0.0001444914232706651</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.0001896623871289194</v>
+        <v>0.0002455536741763353</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.000143599885632284</v>
+        <v>0.0005659215385094285</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.0001283975871047005</v>
+        <v>0.0001184653519885615</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.0007151676691137254</v>
+        <v>0.0002966610190924257</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.0003514423733577132</v>
+        <v>0.000317651400109753</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.000192163250176236</v>
+        <v>0.0003382008871994913</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0002007869188673794</v>
+        <v>0.0004576205974444747</v>
       </c>
       <c r="AG16" t="n">
-        <v>6.382034916896373e-05</v>
+        <v>0.0004058428457938135</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.0001579255767865106</v>
+        <v>2.556684194132686e-06</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.0002659213496372104</v>
+        <v>0.0004191803163848817</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.0001451201969757676</v>
+        <v>0.0003861683362629265</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.0001853542780736461</v>
+        <v>7.99411500338465e-05</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.0006246585980989039</v>
+        <v>0.001070568105205894</v>
       </c>
       <c r="AM16" t="n">
-        <v>4.412811904330738e-06</v>
+        <v>0.0002050090988632292</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.0001417546300217509</v>
+        <v>0.000320464139804244</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.0001810684188967571</v>
+        <v>0.00035134531208314</v>
       </c>
       <c r="AP16" t="n">
-        <v>8.769903797656298e-05</v>
+        <v>0.000158472714247182</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.554188202135265e-06</v>
+        <v>0.0002333738812012598</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.990451710298657e-05</v>
+        <v>0.0002724775695241988</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.000391546287573874</v>
+        <v>0.0001328841026406735</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.0001188768219435588</v>
+        <v>0.0002223027113359421</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.002328423084691167</v>
+        <v>0.003495169803500175</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.0003995274018961936</v>
+        <v>0.0004740735748782754</v>
       </c>
       <c r="AW16" t="n">
-        <v>8.608817734057084e-05</v>
+        <v>0.0001540144585305825</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.0007660094415768981</v>
+        <v>0.0002889074676204473</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.0002923213760368526</v>
+        <v>0.0001296220143558457</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.0002997444535139948</v>
+        <v>2.301577478647232e-05</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.0006079791928641498</v>
+        <v>0.0002579946594778448</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.0002285741793457419</v>
+        <v>3.4626733395271e-05</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.0001077863416867331</v>
+        <v>0.0004929127753712237</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.0003140184562653303</v>
+        <v>0.000747132464312017</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.0006933818804100156</v>
+        <v>0.0006058250437490642</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.0003370646736584604</v>
+        <v>0.0004457584582269192</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.001279184129089117</v>
+        <v>0.00123885425273329</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.0005237337318249047</v>
+        <v>0.0002570256183389574</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.0001986755232792348</v>
+        <v>0.0001154236524598673</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.0001522961392765865</v>
+        <v>0.0002697730087675154</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.0004520810325630009</v>
+        <v>0.0001138289662776515</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.0007226244197227061</v>
+        <v>7.418821041937917e-05</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.0002240711328340694</v>
+        <v>0.0002640752063598484</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.0003448037605267018</v>
+        <v>0.0002144160971511155</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.068224082700908e-05</v>
+        <v>6.083232801756822e-05</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.001103774178773165</v>
+        <v>0.0007668234757147729</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.0003407956101000309</v>
+        <v>0.0001835228322306648</v>
       </c>
       <c r="BR16" t="n">
-        <v>0.0005624489858746529</v>
+        <v>0.000706886756233871</v>
       </c>
       <c r="BS16" t="n">
-        <v>0.0008369488641619682</v>
+        <v>0.0002262792258989066</v>
       </c>
       <c r="BT16" t="n">
-        <v>3.626850229920819e-05</v>
+        <v>0.000309248804114759</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.0001595063804415986</v>
+        <v>0.0005845497362315655</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.001099388464353979</v>
+        <v>0.00220569921657443</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.0007216322119347751</v>
+        <v>0.0001521356170997024</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.0001738216378726065</v>
+        <v>0.0004758829600177705</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.0008294074796140194</v>
+        <v>0.0003003578458447009</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.0007744083995930851</v>
+        <v>3.53202449332457e-06</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.0003060206072404981</v>
+        <v>0.0003570128174033016</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.071644798386842e-05</v>
+        <v>2.648652298375964e-05</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.0002687209052965045</v>
+        <v>0.0003632494772318751</v>
       </c>
       <c r="CD16" t="n">
-        <v>0.0002113850496243685</v>
+        <v>3.86036372219678e-05</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.0004899601917713881</v>
+        <v>0.001207651570439339</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.647373548825271e-05</v>
+        <v>0.0002166357589885592</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.0001247965556103736</v>
+        <v>0.0001571033499203622</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.0001963181712199003</v>
+        <v>0.0002355794131290168</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.0001289905194425955</v>
+        <v>0.0003124595095869154</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0.0002441697288304567</v>
+        <v>6.677105557173491e-05</v>
       </c>
       <c r="CK16" t="n">
-        <v>0.0001010914274957031</v>
+        <v>0.0001424939691787586</v>
       </c>
       <c r="CL16" t="n">
-        <v>0.0001843692880356684</v>
+        <v>0.0001393648126395419</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.0005792363663204014</v>
+        <v>0.0005993755767121911</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.0005459861131384969</v>
+        <v>0.002204183023422956</v>
       </c>
       <c r="CO16" t="n">
-        <v>0.0002599525905679911</v>
+        <v>0.0003755601937882602</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.0003621659707278013</v>
+        <v>0.0009763967827893794</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.0004079086647834629</v>
+        <v>0.0001562947145430371</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.0001468673290219158</v>
+        <v>0.000321996834827587</v>
       </c>
       <c r="CS16" t="n">
-        <v>8.145933679770678e-05</v>
+        <v>0.0001269524072995409</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.362729330547154e-06</v>
+        <v>0.0001077429551514797</v>
       </c>
       <c r="CU16" t="n">
-        <v>0.000269106007181108</v>
+        <v>4.346938658272848e-05</v>
       </c>
       <c r="CV16" t="n">
-        <v>0.0002351995935896412</v>
+        <v>0.0001526102132629603</v>
       </c>
       <c r="CW16" t="n">
-        <v>0.000414143200032413</v>
+        <v>0.001178776612505317</v>
       </c>
       <c r="CX16" t="n">
-        <v>5.038538802182302e-06</v>
+        <v>0.00015113408153411</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.000126938073663041</v>
+        <v>0.0002264435461256653</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.000186411605682224</v>
+        <v>0.0001513039896963164</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.0001813182752812281</v>
+        <v>0.0002959198027383536</v>
       </c>
       <c r="DB16" t="n">
-        <v>0.0002666646905709058</v>
+        <v>1.257925396203063e-05</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.549780037952587e-05</v>
+        <v>0.0001351135579170659</v>
       </c>
       <c r="DD16" t="n">
-        <v>0.0001980165397981182</v>
+        <v>0.0002646770444698632</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.0001504468091297895</v>
+        <v>0.0001861317432485521</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.0006821585702709854</v>
+        <v>0.000618719554040581</v>
       </c>
       <c r="DG16" t="n">
-        <v>0.0002645894710440189</v>
+        <v>5.217637226451188e-05</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.001001633238047361</v>
+        <v>3.587500395951793e-05</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.001208543428219855</v>
+        <v>0.0003401664725970477</v>
       </c>
       <c r="DJ16" t="n">
-        <v>7.726356125203893e-05</v>
+        <v>0.00120445538777858</v>
       </c>
       <c r="DK16" t="n">
-        <v>0.0001139372398029082</v>
+        <v>0.0001094647886930034</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.0003297520743217319</v>
+        <v>1.314302971877623e-05</v>
       </c>
       <c r="DM16" t="n">
-        <v>0.000227872165851295</v>
+        <v>0.0002479111135471612</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.0001336927380179986</v>
+        <v>4.953680036123842e-05</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.000146778256748803</v>
+        <v>0.000703807978425175</v>
       </c>
       <c r="DP16" t="n">
-        <v>2.371630762354471e-05</v>
+        <v>0.0001874751760624349</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.0003387305187061429</v>
+        <v>0.0004426677478477359</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.0001936327898874879</v>
+        <v>4.728763087769039e-05</v>
       </c>
       <c r="DS16" t="n">
-        <v>9.623401274438947e-05</v>
+        <v>0.0001138957450166345</v>
       </c>
       <c r="DT16" t="n">
-        <v>4.124718543607742e-06</v>
+        <v>7.447953976225108e-05</v>
       </c>
       <c r="DU16" t="n">
-        <v>6.807074532844126e-05</v>
+        <v>0.0005952881765551865</v>
       </c>
       <c r="DV16" t="n">
-        <v>0.0002454408095218241</v>
+        <v>0.0004658087273128331</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.0002593372773844749</v>
+        <v>0.0003349392209202051</v>
       </c>
       <c r="DX16" t="n">
-        <v>0.0002013613993767649</v>
+        <v>0.0003905654302798212</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.545740663772449e-05</v>
+        <v>2.155752372345887e-05</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.0001403209316777065</v>
+        <v>0.0001233070361195132</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.0005185318877920508</v>
+        <v>3.958490196964704e-06</v>
       </c>
       <c r="EB16" t="n">
-        <v>7.204434950836003e-07</v>
+        <v>0.0008922339184209704</v>
       </c>
       <c r="EC16" t="n">
-        <v>0.0001608385937288404</v>
+        <v>0.000212106533581391</v>
       </c>
       <c r="ED16" t="n">
-        <v>0.0003720436943694949</v>
+        <v>0.0007893028086982667</v>
       </c>
       <c r="EE16" t="n">
-        <v>9.326876170234755e-05</v>
+        <v>0.0003269183216616511</v>
       </c>
       <c r="EF16" t="n">
-        <v>0.0001450067211408168</v>
+        <v>0.0002444504061713815</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.0003073281841352582</v>
+        <v>0.0007916952599771321</v>
       </c>
       <c r="EH16" t="n">
-        <v>4.001444176537916e-05</v>
+        <v>0.0001666764437686652</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.000173736727447249</v>
+        <v>9.860045975074172e-05</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.000158255803398788</v>
+        <v>5.408348079072312e-05</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.0001615860819583759</v>
+        <v>0.0004628344322554767</v>
       </c>
       <c r="EL16" t="n">
-        <v>0.0004516593762673438</v>
+        <v>8.549086487619206e-06</v>
       </c>
       <c r="EM16" t="n">
-        <v>0.0001602527336217463</v>
+        <v>0.0001625923614483327</v>
       </c>
       <c r="EN16" t="n">
-        <v>0.0002287793322466314</v>
+        <v>7.476126484107226e-05</v>
       </c>
       <c r="EO16" t="n">
-        <v>3.009736974490806e-05</v>
+        <v>0.000111471235868521</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.000520499364938587</v>
+        <v>0.0007967419223859906</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0.0002027924929279834</v>
+        <v>9.408282494405285e-06</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.0001073276944225654</v>
+        <v>7.541378727182746e-05</v>
       </c>
       <c r="ES16" t="n">
-        <v>8.699685167812277e-06</v>
+        <v>0.00023379955382552</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.000420468277297914</v>
+        <v>5.587321356870234e-05</v>
       </c>
       <c r="EU16" t="n">
-        <v>0.0005507127498276532</v>
+        <v>4.165876816841774e-05</v>
       </c>
       <c r="EV16" t="n">
-        <v>0.0004111688758712262</v>
+        <v>0.0001930273429024965</v>
       </c>
       <c r="EW16" t="n">
-        <v>0.0008643317851237953</v>
+        <v>3.720131280715577e-05</v>
       </c>
       <c r="EX16" t="n">
-        <v>0.0001737738639349118</v>
+        <v>5.887986480956897e-05</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.0005327442777343094</v>
+        <v>0.001372258877381682</v>
       </c>
       <c r="EZ16" t="n">
-        <v>9.918215801008046e-05</v>
+        <v>0.0002077831159112975</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.0001868357940111309</v>
+        <v>0.0002091416972689331</v>
       </c>
       <c r="FB16" t="n">
-        <v>9.251331357518211e-05</v>
+        <v>0.0001862488425103948</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.0001941703085321933</v>
+        <v>0.0003156484162900597</v>
       </c>
       <c r="FD16" t="n">
-        <v>0.0002932593051809818</v>
+        <v>7.667405589018017e-05</v>
       </c>
       <c r="FE16" t="n">
-        <v>5.282607162371278e-05</v>
+        <v>2.687788764887955e-05</v>
       </c>
       <c r="FF16" t="n">
-        <v>0.0001680937421042472</v>
+        <v>0.0002568986092228442</v>
       </c>
       <c r="FG16" t="n">
-        <v>0.0003446410410106182</v>
+        <v>0.0002236996369902045</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.0002454308851156384</v>
+        <v>0.00057367910631001</v>
       </c>
       <c r="FI16" t="n">
-        <v>0.0001607360027264804</v>
+        <v>0.0005020963144488633</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.0003151755954604596</v>
+        <v>0.0006228023557923734</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.0006070555537007749</v>
+        <v>0.0001071522274287418</v>
       </c>
       <c r="FL16" t="n">
-        <v>8.220413292292506e-05</v>
+        <v>8.792013977654278e-05</v>
       </c>
       <c r="FM16" t="n">
-        <v>0.000309436465613544</v>
+        <v>0.0002561768342275172</v>
       </c>
       <c r="FN16" t="n">
-        <v>0.000168986662174575</v>
+        <v>0.0001245388411916792</v>
       </c>
       <c r="FO16" t="n">
-        <v>0.0004024838854093105</v>
+        <v>0.0006071703392080963</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.0003062065807171166</v>
+        <v>0.0001182805208372883</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.0004432300920598209</v>
+        <v>0.0006957784062251449</v>
       </c>
       <c r="FR16" t="n">
-        <v>0.0004655091906897724</v>
+        <v>9.232029697159305e-05</v>
       </c>
       <c r="FS16" t="n">
-        <v>0.0001429999829269946</v>
+        <v>0.000486258213641122</v>
       </c>
       <c r="FT16" t="n">
-        <v>9.413560474058613e-05</v>
+        <v>0.0007696507964283228</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.0006545752985402942</v>
+        <v>0.0004281176079530269</v>
       </c>
       <c r="FV16" t="n">
-        <v>0.0001778381993062794</v>
+        <v>4.031222488265485e-05</v>
       </c>
       <c r="FW16" t="n">
-        <v>0.0007341532618738711</v>
+        <v>0.0005870815366506577</v>
       </c>
       <c r="FX16" t="n">
-        <v>0.0003576233284547925</v>
+        <v>0.000679856981150806</v>
       </c>
       <c r="FY16" t="n">
-        <v>0.0003320243558846414</v>
+        <v>0.0001875137677416205</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.0001905409153550863</v>
+        <v>0.0007742403540760279</v>
       </c>
       <c r="GA16" t="n">
-        <v>0.0001745418703649193</v>
+        <v>0.0002192135143559426</v>
       </c>
       <c r="GB16" t="n">
-        <v>0.0001764562912285328</v>
+        <v>0.0001344671036349609</v>
       </c>
       <c r="GC16" t="n">
-        <v>0.0001549720327602699</v>
+        <v>0.000743507465813309</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.0005348482518456876</v>
+        <v>8.576922118663788e-05</v>
       </c>
       <c r="GE16" t="n">
-        <v>0.0007659352850168943</v>
+        <v>0.0002112034271704033</v>
       </c>
       <c r="GF16" t="n">
-        <v>0.0006436946569010615</v>
+        <v>0.0004867639509029686</v>
       </c>
       <c r="GG16" t="n">
-        <v>0.0002628852962516248</v>
+        <v>0.0003200337814632803</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.005096462089568377</v>
+        <v>0.0005659094313159585</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01452082488685846</v>
+        <v>0.0008750189444981515</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0009257447673007846</v>
+        <v>0.0002229841193184257</v>
       </c>
       <c r="D17" t="n">
-        <v>0.001674993894994259</v>
+        <v>0.0002377345226705074</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000941739184781909</v>
+        <v>0.0005299526965245605</v>
       </c>
       <c r="F17" t="n">
-        <v>0.006340477615594864</v>
+        <v>0.0003415928513277322</v>
       </c>
       <c r="G17" t="n">
-        <v>0.003392074722796679</v>
+        <v>0.000122475394164212</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0003247043641749769</v>
+        <v>2.659685196704231e-05</v>
       </c>
       <c r="I17" t="n">
-        <v>0.001472840318456292</v>
+        <v>0.0002272700221510604</v>
       </c>
       <c r="J17" t="n">
-        <v>0.004337824881076813</v>
+        <v>0.0002591274678707123</v>
       </c>
       <c r="K17" t="n">
-        <v>0.01023000199347734</v>
+        <v>0.00142419314943254</v>
       </c>
       <c r="L17" t="n">
-        <v>0.001674646977335215</v>
+        <v>0.000161840405780822</v>
       </c>
       <c r="M17" t="n">
-        <v>0.001156921032816172</v>
+        <v>0.0003979541943408549</v>
       </c>
       <c r="N17" t="n">
-        <v>0.002177807502448559</v>
+        <v>0.000774538260884583</v>
       </c>
       <c r="O17" t="n">
-        <v>0.005850270390510559</v>
+        <v>0.0002254135615658015</v>
       </c>
       <c r="P17" t="n">
-        <v>0.002916292985901237</v>
+        <v>0.0001873321161838248</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.002197500318288803</v>
+        <v>0.0005751021672040224</v>
       </c>
       <c r="R17" t="n">
-        <v>0.002765697194263339</v>
+        <v>0.0003779825055971742</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0001545804407214746</v>
+        <v>4.960288788424805e-05</v>
       </c>
       <c r="T17" t="n">
-        <v>0.002264206996187568</v>
+        <v>0.0002827275602612644</v>
       </c>
       <c r="U17" t="n">
-        <v>0.002255890984088182</v>
+        <v>7.066631951602176e-06</v>
       </c>
       <c r="V17" t="n">
-        <v>0.001442861859686673</v>
+        <v>0.000115569680929184</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0009198497282341123</v>
+        <v>8.629980584373698e-05</v>
       </c>
       <c r="X17" t="n">
-        <v>0.004342800937592983</v>
+        <v>0.000104540515167173</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.001115962048061192</v>
+        <v>3.503406333038583e-05</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.000912324758246541</v>
+        <v>1.234675255545881e-05</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.001193194766528904</v>
+        <v>1.969595541595481e-05</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.0006436843541450799</v>
+        <v>5.923192657064646e-05</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.002828273689374328</v>
+        <v>3.804593507084064e-05</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.002144695026800036</v>
+        <v>0.0002010085590882227</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.0005108289187774062</v>
+        <v>0.0003065792261622846</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0007444171933457255</v>
+        <v>0.0002049337490461767</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.001768668531440198</v>
+        <v>5.183770917938091e-05</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.001835268456488848</v>
+        <v>4.03080994146876e-05</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.0003322549746371806</v>
+        <v>0.0003304285637568682</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.0007006722153164446</v>
+        <v>4.680486745201051e-05</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.0008383343229070306</v>
+        <v>0.000104138562164735</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.002536492887884378</v>
+        <v>0.0003746713045984507</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.0005993495578877628</v>
+        <v>9.875450632534921e-05</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.0004095047479495406</v>
+        <v>2.783280433504842e-05</v>
       </c>
       <c r="AO17" t="n">
-        <v>5.092177161714062e-05</v>
+        <v>0.0001183483982458711</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.00248913443647325</v>
+        <v>0.0001559209922561422</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.0004866714880336076</v>
+        <v>0.0001358419976895675</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.0005315921152941883</v>
+        <v>0.0003152316494379193</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.001201152219437063</v>
+        <v>2.346641849726439e-05</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.001150363241322339</v>
+        <v>2.048984606517479e-05</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.009288445115089417</v>
+        <v>0.00121845630928874</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.0002213424595538527</v>
+        <v>0.0001440516207367182</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.0002153426175937057</v>
+        <v>0.0001040671777445823</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.002624263055622578</v>
+        <v>0.000228595978114754</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.0001763357140589505</v>
+        <v>0.0001148359224316664</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.0003574290312826633</v>
+        <v>1.490161594119854e-07</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.0003757768427021801</v>
+        <v>8.194406109396368e-05</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.001342804986052215</v>
+        <v>7.514277967857197e-06</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.002324854955077171</v>
+        <v>0.0005095291999168694</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.003448975505307317</v>
+        <v>0.0001910826686071232</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.001640480360947549</v>
+        <v>0.0003821872815024108</v>
       </c>
       <c r="BF17" t="n">
-        <v>0.0005370526341721416</v>
+        <v>7.046527025522664e-05</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.002616359619423747</v>
+        <v>0.0003619515337049961</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.004260574001818895</v>
+        <v>9.53463459154591e-05</v>
       </c>
       <c r="BI17" t="n">
-        <v>0.00174826558213681</v>
+        <v>0.0001107941861846484</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.001956050982698798</v>
+        <v>0.0001660088746575639</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.002191226929426193</v>
+        <v>8.237832662416622e-05</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.00123516982421279</v>
+        <v>1.25783626572229e-05</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.001910330378450453</v>
+        <v>0.0001511366135673597</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.0009344645659439266</v>
+        <v>7.380403985735029e-05</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.0006811257917433977</v>
+        <v>1.664336195972282e-05</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.001672972459346056</v>
+        <v>0.000283257570117712</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.00350512657314539</v>
+        <v>0.000217811917536892</v>
       </c>
       <c r="BR17" t="n">
-        <v>0.001283998950384557</v>
+        <v>0.0003430547658354044</v>
       </c>
       <c r="BS17" t="n">
-        <v>0.002212209161370993</v>
+        <v>2.022599437623285e-05</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.002255439525470138</v>
+        <v>4.349178925622255e-05</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.0003824165905825794</v>
+        <v>0.0001965691189980134</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.006030614953488111</v>
+        <v>0.001039719209074974</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.0008952255011536181</v>
+        <v>0.0001239528355654329</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.002131470246240497</v>
+        <v>0.0001649358164286241</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.001102924579754472</v>
+        <v>0.0001033192384056747</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.002735476708039641</v>
+        <v>7.029904372757301e-05</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.0008960614795796573</v>
+        <v>0.0002093314978992566</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.0006349622271955013</v>
+        <v>0.0001738713763188571</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.0005678322049789131</v>
+        <v>8.318905747728422e-05</v>
       </c>
       <c r="CD17" t="n">
-        <v>0.001242568250745535</v>
+        <v>0.0001010664709610865</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.001829162007197738</v>
+        <v>0.0003025869955308735</v>
       </c>
       <c r="CF17" t="n">
-        <v>0.0003689855802804232</v>
+        <v>8.292954589705914e-05</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.000632608775049448</v>
+        <v>7.862047641538084e-05</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.001404861453920603</v>
+        <v>0.0001021231146296486</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.001540221739560366</v>
+        <v>9.221924847224727e-05</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0.0001039346243487671</v>
+        <v>1.015296220430173e-06</v>
       </c>
       <c r="CK17" t="n">
-        <v>0.0003173333825543523</v>
+        <v>1.4636634659837e-07</v>
       </c>
       <c r="CL17" t="n">
-        <v>8.048550807870924e-05</v>
+        <v>6.701204256387427e-05</v>
       </c>
       <c r="CM17" t="n">
-        <v>0.0007563268882222474</v>
+        <v>0.0002507804310880601</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.001541835255920887</v>
+        <v>0.0008104756125248969</v>
       </c>
       <c r="CO17" t="n">
-        <v>0.0009865931933745742</v>
+        <v>6.969462265260518e-05</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.0002072507631964982</v>
+        <v>9.985207725549117e-05</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.003076067892834544</v>
+        <v>0.000167934107594192</v>
       </c>
       <c r="CR17" t="n">
-        <v>0.0004860771005041897</v>
+        <v>0.000195114262169227</v>
       </c>
       <c r="CS17" t="n">
-        <v>0.00154484563972801</v>
+        <v>0.0002185559424106032</v>
       </c>
       <c r="CT17" t="n">
-        <v>0.0009016319527290761</v>
+        <v>0.0003087511286139488</v>
       </c>
       <c r="CU17" t="n">
-        <v>0.001209879177622497</v>
+        <v>3.128972457488999e-05</v>
       </c>
       <c r="CV17" t="n">
-        <v>0.0006116810254752636</v>
+        <v>2.04370662686415e-05</v>
       </c>
       <c r="CW17" t="n">
-        <v>0.001975019229575992</v>
+        <v>0.0003110213729087263</v>
       </c>
       <c r="CX17" t="n">
-        <v>0.0004438167670741677</v>
+        <v>7.363912300206721e-05</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.0006268426077440381</v>
+        <v>4.365315544418991e-05</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.001020957133732736</v>
+        <v>2.955164745799266e-05</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.002842637477442622</v>
+        <v>6.620022031711414e-05</v>
       </c>
       <c r="DB17" t="n">
-        <v>0.0002141429140465334</v>
+        <v>4.676590469898656e-05</v>
       </c>
       <c r="DC17" t="n">
-        <v>0.0002919842081610113</v>
+        <v>8.867871656548232e-06</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.819421595428139e-05</v>
+        <v>5.739543485105969e-05</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.001530601643025875</v>
+        <v>1.317539135925472e-05</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.004220990929752588</v>
+        <v>0.0006650303257629275</v>
       </c>
       <c r="DG17" t="n">
-        <v>0.001858257572166622</v>
+        <v>2.947432221844792e-05</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.002234314568340778</v>
+        <v>3.76324460376054e-05</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.004928800277411938</v>
+        <v>1.85615735972533e-05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.00473423209041357</v>
+        <v>8.751643326831982e-05</v>
       </c>
       <c r="DK17" t="n">
-        <v>0.000317342288326472</v>
+        <v>4.703506419900805e-06</v>
       </c>
       <c r="DL17" t="n">
-        <v>2.563487214501947e-06</v>
+        <v>0.0001414230646332726</v>
       </c>
       <c r="DM17" t="n">
-        <v>0.002382416510954499</v>
+        <v>0.0001201818959088996</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.0004794494598172605</v>
+        <v>0.0001007057289825752</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.414494520053267e-05</v>
+        <v>0.000142851029522717</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.0006338655948638916</v>
+        <v>1.998290463234298e-05</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.00195042381528765</v>
+        <v>1.61363605002407e-05</v>
       </c>
       <c r="DR17" t="n">
-        <v>1.094619801733643e-05</v>
+        <v>0.0001050885693985038</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.0003616630856413394</v>
+        <v>3.447368726483546e-05</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.0003972184204030782</v>
+        <v>8.428278306382708e-07</v>
       </c>
       <c r="DU17" t="n">
-        <v>0.001256697112694383</v>
+        <v>0.0001021057250909507</v>
       </c>
       <c r="DV17" t="n">
-        <v>0.001971959136426449</v>
+        <v>7.738528438494541e-06</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.0006800915580242872</v>
+        <v>0.0002260194451082498</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.001162219210527837</v>
+        <v>0.0003670791629701853</v>
       </c>
       <c r="DY17" t="n">
-        <v>0.001226567663252354</v>
+        <v>5.679234163835645e-06</v>
       </c>
       <c r="DZ17" t="n">
-        <v>0.0007439870969392359</v>
+        <v>7.553812611149624e-05</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.0003576047893147916</v>
+        <v>0.0001161861582659185</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.00253986893221736</v>
+        <v>9.051247616298497e-06</v>
       </c>
       <c r="EC17" t="n">
-        <v>6.668528658337891e-05</v>
+        <v>3.378827386768535e-05</v>
       </c>
       <c r="ED17" t="n">
-        <v>0.0007867139647714794</v>
+        <v>2.405310442554764e-05</v>
       </c>
       <c r="EE17" t="n">
-        <v>0.001415924169123173</v>
+        <v>0.0001714384852675721</v>
       </c>
       <c r="EF17" t="n">
-        <v>0.0001333153049927205</v>
+        <v>3.379257395863533e-05</v>
       </c>
       <c r="EG17" t="n">
-        <v>0.0005641237366944551</v>
+        <v>1.160028114099987e-05</v>
       </c>
       <c r="EH17" t="n">
-        <v>0.000407014274969697</v>
+        <v>2.040634717559442e-05</v>
       </c>
       <c r="EI17" t="n">
-        <v>0.001468521310016513</v>
+        <v>0.000109049811726436</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.001137910527177155</v>
+        <v>1.76913345057983e-05</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.003508308669552207</v>
+        <v>0.0001589564781170338</v>
       </c>
       <c r="EL17" t="n">
-        <v>0.0004830615362152457</v>
+        <v>6.779566319892183e-06</v>
       </c>
       <c r="EM17" t="n">
-        <v>4.760501178679988e-05</v>
+        <v>1.896064713946544e-05</v>
       </c>
       <c r="EN17" t="n">
-        <v>0.0002444314595777541</v>
+        <v>7.765883492538705e-05</v>
       </c>
       <c r="EO17" t="n">
-        <v>0.0005322230281308293</v>
+        <v>0.0001759949664119631</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.001976479310542345</v>
+        <v>4.682772851083428e-05</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0.0003987998061347753</v>
+        <v>8.617564162705094e-05</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.0009628940606489778</v>
+        <v>0.0001137630897574127</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.00125376577489078</v>
+        <v>0.000247945892624557</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.00365735124796629</v>
+        <v>7.142545655369759e-06</v>
       </c>
       <c r="EU17" t="n">
-        <v>0.000104966398794204</v>
+        <v>0.0001187902234960347</v>
       </c>
       <c r="EV17" t="n">
-        <v>0.002013314748182893</v>
+        <v>3.032619861187413e-05</v>
       </c>
       <c r="EW17" t="n">
-        <v>0.0009072042885236442</v>
+        <v>5.884217171114869e-05</v>
       </c>
       <c r="EX17" t="n">
-        <v>0.0008201942546293139</v>
+        <v>6.905773625476286e-05</v>
       </c>
       <c r="EY17" t="n">
-        <v>0.002275896025821567</v>
+        <v>0.0003842873265966773</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0.0003638849884737283</v>
+        <v>6.419247802114114e-05</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.0008555224630981684</v>
+        <v>5.697944652638398e-05</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.001872364897280931</v>
+        <v>2.363514067837968e-05</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.002296597231179476</v>
+        <v>6.877161649754271e-05</v>
       </c>
       <c r="FD17" t="n">
-        <v>9.906268678605556e-05</v>
+        <v>1.956561754923314e-05</v>
       </c>
       <c r="FE17" t="n">
-        <v>0.0002030163304880261</v>
+        <v>2.875603786378633e-05</v>
       </c>
       <c r="FF17" t="n">
-        <v>0.0002601180167403072</v>
+        <v>9.825445886235684e-05</v>
       </c>
       <c r="FG17" t="n">
-        <v>4.1089893784374e-05</v>
+        <v>2.885959111154079e-05</v>
       </c>
       <c r="FH17" t="n">
-        <v>0.000905168941244483</v>
+        <v>0.0002080910635413602</v>
       </c>
       <c r="FI17" t="n">
-        <v>0.0001835149305406958</v>
+        <v>2.201545066782273e-05</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.001673851627856493</v>
+        <v>0.0001396143634337932</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.001387950265780091</v>
+        <v>0.000336798868374899</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.001385065610520542</v>
+        <v>6.188053521327674e-05</v>
       </c>
       <c r="FM17" t="n">
-        <v>0.001567155006341636</v>
+        <v>8.993859228212386e-05</v>
       </c>
       <c r="FN17" t="n">
-        <v>0.0004149394808337092</v>
+        <v>0.0002268238895339891</v>
       </c>
       <c r="FO17" t="n">
-        <v>0.0008589130593463778</v>
+        <v>5.676130967913195e-05</v>
       </c>
       <c r="FP17" t="n">
-        <v>0.001662649912759662</v>
+        <v>5.022144614486024e-05</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.003932030405849218</v>
+        <v>2.32042875722982e-05</v>
       </c>
       <c r="FR17" t="n">
-        <v>0.00126069167163223</v>
+        <v>3.482362808426842e-05</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.002149239415302873</v>
+        <v>0.000145848243846558</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.000188711826922372</v>
+        <v>0.001079610083252192</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.0007708329358138144</v>
+        <v>0.0001647502358537167</v>
       </c>
       <c r="FV17" t="n">
-        <v>0.0007451046258211136</v>
+        <v>8.40922148199752e-05</v>
       </c>
       <c r="FW17" t="n">
-        <v>0.001742690103128552</v>
+        <v>9.168325050268322e-06</v>
       </c>
       <c r="FX17" t="n">
-        <v>0.001231344416737556</v>
+        <v>0.0001529664878034964</v>
       </c>
       <c r="FY17" t="n">
-        <v>0.001220005331560969</v>
+        <v>9.522204345557839e-05</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.001132052508182824</v>
+        <v>0.0002291115961270407</v>
       </c>
       <c r="GA17" t="n">
-        <v>0.0004679912817664444</v>
+        <v>5.947702447883785e-05</v>
       </c>
       <c r="GB17" t="n">
-        <v>0.0008807388367131352</v>
+        <v>0.0002020543324761093</v>
       </c>
       <c r="GC17" t="n">
-        <v>0.007243209518492222</v>
+        <v>0.0002405234408797696</v>
       </c>
       <c r="GD17" t="n">
-        <v>0.001765634515322745</v>
+        <v>0.0002120617136824876</v>
       </c>
       <c r="GE17" t="n">
-        <v>0.005996008403599262</v>
+        <v>0.0001455377787351608</v>
       </c>
       <c r="GF17" t="n">
-        <v>0.000126754748634994</v>
+        <v>0.0001487681438447908</v>
       </c>
       <c r="GG17" t="n">
-        <v>0.00129481207113713</v>
+        <v>3.245545667596161e-05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5.398706889536697e-06</v>
+        <v>0.2260994911193848</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0001701334986137226</v>
+        <v>0.8281870484352112</v>
       </c>
       <c r="C18" t="n">
-        <v>2.589160430943593e-05</v>
+        <v>0.05392694473266602</v>
       </c>
       <c r="D18" t="n">
-        <v>5.97347752773203e-06</v>
+        <v>0.01955033466219902</v>
       </c>
       <c r="E18" t="n">
-        <v>3.953740088036284e-05</v>
+        <v>0.7017801403999329</v>
       </c>
       <c r="F18" t="n">
-        <v>3.02100415865425e-05</v>
+        <v>0.5383400917053223</v>
       </c>
       <c r="G18" t="n">
-        <v>8.107529720291495e-05</v>
+        <v>0.02743701636791229</v>
       </c>
       <c r="H18" t="n">
-        <v>3.872156867146259e-06</v>
+        <v>0.005519717931747437</v>
       </c>
       <c r="I18" t="n">
-        <v>4.353209988039453e-06</v>
+        <v>0.3326360881328583</v>
       </c>
       <c r="J18" t="n">
-        <v>5.960046109976247e-06</v>
+        <v>0.3511799275875092</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0001316095440415666</v>
+        <v>1.119663119316101</v>
       </c>
       <c r="L18" t="n">
-        <v>1.020063245960046e-05</v>
+        <v>0.1346198618412018</v>
       </c>
       <c r="M18" t="n">
-        <v>6.175755697768182e-05</v>
+        <v>0.2199408113956451</v>
       </c>
       <c r="N18" t="n">
-        <v>3.867164923576638e-05</v>
+        <v>1.057914018630981</v>
       </c>
       <c r="O18" t="n">
-        <v>2.195417255279608e-05</v>
+        <v>0.6749969720840454</v>
       </c>
       <c r="P18" t="n">
-        <v>6.967773515498266e-05</v>
+        <v>0.1535580456256866</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.646612145123072e-05</v>
+        <v>0.3648690283298492</v>
       </c>
       <c r="R18" t="n">
-        <v>6.034300895407796e-06</v>
+        <v>0.4132764637470245</v>
       </c>
       <c r="S18" t="n">
-        <v>5.551737558562309e-06</v>
+        <v>0.2343072295188904</v>
       </c>
       <c r="T18" t="n">
-        <v>4.775061825057492e-05</v>
+        <v>0.3196750283241272</v>
       </c>
       <c r="U18" t="n">
-        <v>6.863966518722009e-06</v>
+        <v>0.03277843073010445</v>
       </c>
       <c r="V18" t="n">
-        <v>2.634279007907026e-05</v>
+        <v>0.1390950828790665</v>
       </c>
       <c r="W18" t="n">
-        <v>4.581758184940554e-05</v>
+        <v>0.06146173179149628</v>
       </c>
       <c r="X18" t="n">
-        <v>2.880063948396128e-05</v>
+        <v>0.1327257454395294</v>
       </c>
       <c r="Y18" t="n">
-        <v>7.004196049820166e-07</v>
+        <v>0.07693527638912201</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.640043956285808e-05</v>
+        <v>0.2659407258033752</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.679835107410327e-06</v>
+        <v>0.06737304478883743</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.596399826870766e-05</v>
+        <v>0.3684146404266357</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.851551082334481e-05</v>
+        <v>0.0781840980052948</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.009042898658663e-05</v>
+        <v>0.1573654413223267</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.225923824677011e-06</v>
+        <v>0.09885390102863312</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.997187377535738e-06</v>
+        <v>0.442432165145874</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.853098001447506e-05</v>
+        <v>0.3136702477931976</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.783665197763185e-07</v>
+        <v>0.07389505952596664</v>
       </c>
       <c r="AI18" t="n">
-        <v>7.278834345925134e-06</v>
+        <v>0.3703822493553162</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.591552402009256e-06</v>
+        <v>0.04087924212217331</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.217720611952245e-05</v>
+        <v>0.2045647501945496</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.081664504454238e-05</v>
+        <v>0.3510442078113556</v>
       </c>
       <c r="AM18" t="n">
-        <v>2.40712165577861e-06</v>
+        <v>0.0760224312543869</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.520090154372156e-05</v>
+        <v>0.01743809133768082</v>
       </c>
       <c r="AO18" t="n">
-        <v>6.966692126297858e-06</v>
+        <v>0.08269133418798447</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.546121893625241e-05</v>
+        <v>0.08977679908275604</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7.663322321604937e-06</v>
+        <v>0.03445570915937424</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.626734956516884e-06</v>
+        <v>0.3528801798820496</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.745593171013752e-06</v>
+        <v>0.04229339584708214</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.727833089011256e-05</v>
+        <v>0.2417357861995697</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.0001280023425351828</v>
+        <v>1.132926106452942</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.610647586858249e-06</v>
+        <v>0.03446590900421143</v>
       </c>
       <c r="AW18" t="n">
-        <v>3.497651778161526e-05</v>
+        <v>0.1242323368787766</v>
       </c>
       <c r="AX18" t="n">
-        <v>8.343131412402727e-06</v>
+        <v>0.2464496493339539</v>
       </c>
       <c r="AY18" t="n">
-        <v>2.138652234862093e-05</v>
+        <v>0.4765160083770752</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.208235623082146e-05</v>
+        <v>0.04441655054688454</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.896545993280597e-06</v>
+        <v>0.02573633939027786</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.118751348869409e-06</v>
+        <v>0.1179349645972252</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.854059286823031e-06</v>
+        <v>0.05458240211009979</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.063760909251869e-05</v>
+        <v>0.3583347797393799</v>
       </c>
       <c r="BE18" t="n">
-        <v>3.082049079239368e-05</v>
+        <v>0.04149875789880753</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.691468969511334e-05</v>
+        <v>0.01344310492277145</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.117909414460883e-05</v>
+        <v>0.2443744689226151</v>
       </c>
       <c r="BH18" t="n">
-        <v>1.473100928706117e-05</v>
+        <v>0.1561374366283417</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.142011726391502e-05</v>
+        <v>0.1120516508817673</v>
       </c>
       <c r="BJ18" t="n">
-        <v>2.311714524694253e-06</v>
+        <v>0.1004181355237961</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.149401850852882e-05</v>
+        <v>0.02772320806980133</v>
       </c>
       <c r="BL18" t="n">
-        <v>9.660508112574462e-06</v>
+        <v>0.05991809070110321</v>
       </c>
       <c r="BM18" t="n">
-        <v>3.921624374925159e-05</v>
+        <v>0.1498366743326187</v>
       </c>
       <c r="BN18" t="n">
-        <v>2.557226616772823e-05</v>
+        <v>0.05330178886651993</v>
       </c>
       <c r="BO18" t="n">
-        <v>2.281614251842257e-05</v>
+        <v>0.1730035990476608</v>
       </c>
       <c r="BP18" t="n">
-        <v>6.241426308406517e-05</v>
+        <v>0.4093134105205536</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.409505784977227e-05</v>
+        <v>0.3321793377399445</v>
       </c>
       <c r="BR18" t="n">
-        <v>7.12264773028437e-06</v>
+        <v>0.08115030080080032</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.359271118417382e-05</v>
+        <v>0.07274927198886871</v>
       </c>
       <c r="BT18" t="n">
-        <v>3.147225015709409e-06</v>
+        <v>0.08213073015213013</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.177735884994036e-05</v>
+        <v>0.2812659442424774</v>
       </c>
       <c r="BV18" t="n">
-        <v>6.026444316376001e-05</v>
+        <v>0.9504214525222778</v>
       </c>
       <c r="BW18" t="n">
-        <v>2.834707265719771e-05</v>
+        <v>0.1966835856437683</v>
       </c>
       <c r="BX18" t="n">
-        <v>2.96578582492657e-05</v>
+        <v>0.270143985748291</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.138834795710864e-05</v>
+        <v>0.1681308597326279</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.376735028519761e-05</v>
+        <v>0.2572726309299469</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.785390850272961e-05</v>
+        <v>0.1228465214371681</v>
       </c>
       <c r="CB18" t="n">
-        <v>1.688887277850881e-05</v>
+        <v>0.003262355923652649</v>
       </c>
       <c r="CC18" t="n">
-        <v>1.327678091911366e-07</v>
+        <v>0.15227110683918</v>
       </c>
       <c r="CD18" t="n">
-        <v>4.959612851962447e-06</v>
+        <v>0.156419575214386</v>
       </c>
       <c r="CE18" t="n">
-        <v>3.449357609497383e-05</v>
+        <v>0.3609298467636108</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.386523192399181e-06</v>
+        <v>0.02368327975273132</v>
       </c>
       <c r="CG18" t="n">
-        <v>9.015521754918154e-06</v>
+        <v>0.100988358259201</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.646201212679443e-06</v>
+        <v>0.2434675991535187</v>
       </c>
       <c r="CI18" t="n">
-        <v>3.402836910026963e-06</v>
+        <v>0.1685074716806412</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.373212671751389e-05</v>
+        <v>0.02487456426024437</v>
       </c>
       <c r="CK18" t="n">
-        <v>2.201593360950937e-06</v>
+        <v>0.0754607692360878</v>
       </c>
       <c r="CL18" t="n">
-        <v>6.812284709667438e-07</v>
+        <v>0.0667140930891037</v>
       </c>
       <c r="CM18" t="n">
-        <v>3.954713611165062e-05</v>
+        <v>0.1027891933917999</v>
       </c>
       <c r="CN18" t="n">
-        <v>5.562650767387822e-05</v>
+        <v>0.6524562835693359</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.298072675126605e-06</v>
+        <v>0.04968447238206863</v>
       </c>
       <c r="CP18" t="n">
-        <v>4.907263246423099e-06</v>
+        <v>0.4509775638580322</v>
       </c>
       <c r="CQ18" t="n">
-        <v>6.481770833488554e-05</v>
+        <v>0.09095557034015656</v>
       </c>
       <c r="CR18" t="n">
-        <v>3.48960020346567e-05</v>
+        <v>0.06504438072443008</v>
       </c>
       <c r="CS18" t="n">
-        <v>1.309306207986083e-05</v>
+        <v>0.06835172325372696</v>
       </c>
       <c r="CT18" t="n">
-        <v>9.436894288228359e-06</v>
+        <v>0.1303896009922028</v>
       </c>
       <c r="CU18" t="n">
-        <v>2.528785444155801e-05</v>
+        <v>0.01237417384982109</v>
       </c>
       <c r="CV18" t="n">
-        <v>7.620062206115108e-06</v>
+        <v>0.0816868469119072</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.67479208559962e-05</v>
+        <v>0.3234639465808868</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.108016567741288e-05</v>
+        <v>0.009630724787712097</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.643181894905865e-05</v>
+        <v>0.1766014248132706</v>
       </c>
       <c r="CZ18" t="n">
-        <v>4.214321904782992e-07</v>
+        <v>0.2111124396324158</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.519215513530071e-06</v>
+        <v>0.1879944205284119</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.160779629572062e-05</v>
+        <v>0.04421724379062653</v>
       </c>
       <c r="DC18" t="n">
-        <v>3.207506551916595e-06</v>
+        <v>0.1095681563019753</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.276031298402813e-06</v>
+        <v>0.08016057312488556</v>
       </c>
       <c r="DE18" t="n">
-        <v>1.640818481973838e-05</v>
+        <v>0.01425917446613312</v>
       </c>
       <c r="DF18" t="n">
-        <v>9.595372102921829e-05</v>
+        <v>0.4607200026512146</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.943810795841273e-05</v>
+        <v>0.00303986668586731</v>
       </c>
       <c r="DH18" t="n">
-        <v>1.878701004898176e-05</v>
+        <v>0.08490445464849472</v>
       </c>
       <c r="DI18" t="n">
-        <v>1.936489024956245e-05</v>
+        <v>0.158826157450676</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.270353979838546e-05</v>
+        <v>0.2204921692609787</v>
       </c>
       <c r="DK18" t="n">
-        <v>1.422186869604047e-05</v>
+        <v>0.1031866744160652</v>
       </c>
       <c r="DL18" t="n">
-        <v>1.113202324631857e-05</v>
+        <v>0.2647860646247864</v>
       </c>
       <c r="DM18" t="n">
-        <v>2.498074718459975e-05</v>
+        <v>0.07464951276779175</v>
       </c>
       <c r="DN18" t="n">
-        <v>9.043717000167817e-06</v>
+        <v>0.1190391182899475</v>
       </c>
       <c r="DO18" t="n">
-        <v>3.346415178384632e-05</v>
+        <v>0.1441310346126556</v>
       </c>
       <c r="DP18" t="n">
-        <v>8.788509148871526e-06</v>
+        <v>0.03702143952250481</v>
       </c>
       <c r="DQ18" t="n">
-        <v>1.063553827407304e-05</v>
+        <v>0.1771582961082458</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.949869657546515e-06</v>
+        <v>0.2722383737564087</v>
       </c>
       <c r="DS18" t="n">
-        <v>9.174596925731748e-06</v>
+        <v>0.1934257000684738</v>
       </c>
       <c r="DT18" t="n">
-        <v>1.840869481384289e-05</v>
+        <v>0.09331168234348297</v>
       </c>
       <c r="DU18" t="n">
-        <v>7.892111170804128e-06</v>
+        <v>0.2339181751012802</v>
       </c>
       <c r="DV18" t="n">
-        <v>8.793030247034039e-06</v>
+        <v>0.1651138812303543</v>
       </c>
       <c r="DW18" t="n">
-        <v>8.759634511079639e-07</v>
+        <v>0.1657560467720032</v>
       </c>
       <c r="DX18" t="n">
-        <v>2.052308991551399e-05</v>
+        <v>0.3059813380241394</v>
       </c>
       <c r="DY18" t="n">
-        <v>5.000496912543895e-06</v>
+        <v>0.08128936588764191</v>
       </c>
       <c r="DZ18" t="n">
-        <v>1.439155767002376e-05</v>
+        <v>0.04586588591337204</v>
       </c>
       <c r="EA18" t="n">
-        <v>2.786322511383332e-05</v>
+        <v>0.1998011916875839</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.596896618138999e-05</v>
+        <v>0.1482878178358078</v>
       </c>
       <c r="EC18" t="n">
-        <v>6.386061613739002e-06</v>
+        <v>0.0459560826420784</v>
       </c>
       <c r="ED18" t="n">
-        <v>1.667302285568439e-06</v>
+        <v>0.004654122516512871</v>
       </c>
       <c r="EE18" t="n">
-        <v>4.367196197563317e-06</v>
+        <v>0.452820748090744</v>
       </c>
       <c r="EF18" t="n">
-        <v>1.61407733685337e-05</v>
+        <v>0.01374697685241699</v>
       </c>
       <c r="EG18" t="n">
-        <v>9.502798093308229e-06</v>
+        <v>0.1211285889148712</v>
       </c>
       <c r="EH18" t="n">
-        <v>2.949432428067666e-06</v>
+        <v>0.07441487908363342</v>
       </c>
       <c r="EI18" t="n">
-        <v>3.527346780174412e-05</v>
+        <v>0.07480394095182419</v>
       </c>
       <c r="EJ18" t="n">
-        <v>8.819518370728474e-06</v>
+        <v>0.08963429182767868</v>
       </c>
       <c r="EK18" t="n">
-        <v>3.343410298839444e-06</v>
+        <v>0.2313106954097748</v>
       </c>
       <c r="EL18" t="n">
-        <v>1.01830610219622e-05</v>
+        <v>0.0760624036192894</v>
       </c>
       <c r="EM18" t="n">
-        <v>6.992698899921379e-07</v>
+        <v>0.08878844976425171</v>
       </c>
       <c r="EN18" t="n">
-        <v>6.464650255111337e-07</v>
+        <v>0.07914168387651443</v>
       </c>
       <c r="EO18" t="n">
-        <v>1.651973252592143e-05</v>
+        <v>0.1007655635476112</v>
       </c>
       <c r="EP18" t="n">
-        <v>6.166460480017122e-06</v>
+        <v>0.209413930773735</v>
       </c>
       <c r="EQ18" t="n">
-        <v>1.742235144774895e-05</v>
+        <v>0.04169151932001114</v>
       </c>
       <c r="ER18" t="n">
-        <v>1.575316673552152e-05</v>
+        <v>0.2431246638298035</v>
       </c>
       <c r="ES18" t="n">
-        <v>1.116227576858364e-05</v>
+        <v>0.04311555996537209</v>
       </c>
       <c r="ET18" t="n">
-        <v>2.656683136592619e-06</v>
+        <v>0.07577234506607056</v>
       </c>
       <c r="EU18" t="n">
-        <v>4.176684342382941e-06</v>
+        <v>0.05799388885498047</v>
       </c>
       <c r="EV18" t="n">
-        <v>1.480334617554036e-06</v>
+        <v>0.08423983305692673</v>
       </c>
       <c r="EW18" t="n">
-        <v>2.000642325583613e-06</v>
+        <v>0.01421879045665264</v>
       </c>
       <c r="EX18" t="n">
-        <v>7.670948434679303e-06</v>
+        <v>0.1320495158433914</v>
       </c>
       <c r="EY18" t="n">
-        <v>2.735355337790679e-05</v>
+        <v>0.3856686949729919</v>
       </c>
       <c r="EZ18" t="n">
-        <v>4.761916898132768e-06</v>
+        <v>0.005964754149317741</v>
       </c>
       <c r="FA18" t="n">
-        <v>1.154731580754742e-05</v>
+        <v>0.1317620277404785</v>
       </c>
       <c r="FB18" t="n">
-        <v>2.18358604797686e-06</v>
+        <v>0.1631848812103271</v>
       </c>
       <c r="FC18" t="n">
-        <v>6.509535069199046e-06</v>
+        <v>0.1405971944332123</v>
       </c>
       <c r="FD18" t="n">
-        <v>1.224784136866219e-05</v>
+        <v>0.02955600619316101</v>
       </c>
       <c r="FE18" t="n">
-        <v>6.595845661649946e-06</v>
+        <v>0.1542651653289795</v>
       </c>
       <c r="FF18" t="n">
-        <v>5.355789198802086e-07</v>
+        <v>0.134689062833786</v>
       </c>
       <c r="FG18" t="n">
-        <v>9.506155947747175e-06</v>
+        <v>0.06965547800064087</v>
       </c>
       <c r="FH18" t="n">
-        <v>3.160843334626406e-06</v>
+        <v>0.1546080261468887</v>
       </c>
       <c r="FI18" t="n">
-        <v>4.515286491368897e-06</v>
+        <v>0.04193835332989693</v>
       </c>
       <c r="FJ18" t="n">
-        <v>1.14582526293816e-05</v>
+        <v>0.3309506773948669</v>
       </c>
       <c r="FK18" t="n">
-        <v>3.039612420252524e-05</v>
+        <v>0.0183066613972187</v>
       </c>
       <c r="FL18" t="n">
-        <v>1.986770439543761e-05</v>
+        <v>0.07834832370281219</v>
       </c>
       <c r="FM18" t="n">
-        <v>7.340208867390174e-06</v>
+        <v>0.2010427862405777</v>
       </c>
       <c r="FN18" t="n">
-        <v>1.026860081765335e-05</v>
+        <v>0.07025653123855591</v>
       </c>
       <c r="FO18" t="n">
-        <v>4.279809218132868e-06</v>
+        <v>0.06691312789916992</v>
       </c>
       <c r="FP18" t="n">
-        <v>1.188237183669116e-05</v>
+        <v>0.1524829268455505</v>
       </c>
       <c r="FQ18" t="n">
-        <v>2.219252928625792e-05</v>
+        <v>0.1231459826231003</v>
       </c>
       <c r="FR18" t="n">
-        <v>1.195840013679117e-05</v>
+        <v>0.1219900697469711</v>
       </c>
       <c r="FS18" t="n">
-        <v>3.646427285275422e-05</v>
+        <v>0.4098575711250305</v>
       </c>
       <c r="FT18" t="n">
-        <v>7.653775355720427e-06</v>
+        <v>0.1721003502607346</v>
       </c>
       <c r="FU18" t="n">
-        <v>1.062970795828733e-06</v>
+        <v>0.1285487413406372</v>
       </c>
       <c r="FV18" t="n">
-        <v>2.879111343645491e-05</v>
+        <v>0.09353923797607422</v>
       </c>
       <c r="FW18" t="n">
-        <v>3.25471737596672e-05</v>
+        <v>0.2217815965414047</v>
       </c>
       <c r="FX18" t="n">
-        <v>8.425331543548964e-08</v>
+        <v>0.1517863571643829</v>
       </c>
       <c r="FY18" t="n">
-        <v>7.04646845406387e-06</v>
+        <v>0.2774087488651276</v>
       </c>
       <c r="FZ18" t="n">
-        <v>2.096716161759105e-05</v>
+        <v>0.1690239310264587</v>
       </c>
       <c r="GA18" t="n">
-        <v>1.667060132604092e-05</v>
+        <v>0.0723181739449501</v>
       </c>
       <c r="GB18" t="n">
-        <v>2.046216832241043e-05</v>
+        <v>0.1274771690368652</v>
       </c>
       <c r="GC18" t="n">
-        <v>8.850494850776158e-06</v>
+        <v>0.1062582433223724</v>
       </c>
       <c r="GD18" t="n">
-        <v>1.391830664942972e-05</v>
+        <v>0.3374999463558197</v>
       </c>
       <c r="GE18" t="n">
-        <v>9.219809726346284e-06</v>
+        <v>0.1183241158723831</v>
       </c>
       <c r="GF18" t="n">
-        <v>2.388520806562155e-05</v>
+        <v>0.1339783221483231</v>
       </c>
       <c r="GG18" t="n">
-        <v>2.994071337525384e-06</v>
+        <v>0.1930817365646362</v>
       </c>
     </row>
     <row r="19">
@@ -11241,571 +11241,571 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.003691310063004494</v>
+        <v>0.009833017364144325</v>
       </c>
       <c r="B20" t="n">
-        <v>0.03285301849246025</v>
+        <v>0.08299810439348221</v>
       </c>
       <c r="C20" t="n">
-        <v>0.009637106209993362</v>
+        <v>0.03686355426907539</v>
       </c>
       <c r="D20" t="n">
-        <v>0.00437565054744482</v>
+        <v>0.03521646559238434</v>
       </c>
       <c r="E20" t="n">
-        <v>0.06435952335596085</v>
+        <v>0.04870659485459328</v>
       </c>
       <c r="F20" t="n">
-        <v>0.009351183660328388</v>
+        <v>0.05391603708267212</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0246356800198555</v>
+        <v>0.002619946375489235</v>
       </c>
       <c r="H20" t="n">
-        <v>0.01915368624031544</v>
+        <v>0.05632400512695312</v>
       </c>
       <c r="I20" t="n">
-        <v>0.009005802683532238</v>
+        <v>0.005705167539417744</v>
       </c>
       <c r="J20" t="n">
-        <v>0.009018959477543831</v>
+        <v>0.0179845504462719</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0187781285494566</v>
+        <v>0.08778173476457596</v>
       </c>
       <c r="L20" t="n">
-        <v>0.004888697527348995</v>
+        <v>0.03177230432629585</v>
       </c>
       <c r="M20" t="n">
-        <v>0.003046846017241478</v>
+        <v>0.07385306805372238</v>
       </c>
       <c r="N20" t="n">
-        <v>0.05590394511818886</v>
+        <v>0.07488519698381424</v>
       </c>
       <c r="O20" t="n">
-        <v>0.006198430433869362</v>
+        <v>0.03007200360298157</v>
       </c>
       <c r="P20" t="n">
-        <v>0.01239414885640144</v>
+        <v>0.002636499237269163</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.02138173580169678</v>
+        <v>0.03737520053982735</v>
       </c>
       <c r="R20" t="n">
-        <v>0.01504057459533215</v>
+        <v>0.005611893255263567</v>
       </c>
       <c r="S20" t="n">
-        <v>0.005156927742063999</v>
+        <v>0.009568352252244949</v>
       </c>
       <c r="T20" t="n">
-        <v>0.002546505304053426</v>
+        <v>0.01514619030058384</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0045714913867414</v>
+        <v>0.004445286002010107</v>
       </c>
       <c r="V20" t="n">
-        <v>0.009894684888422489</v>
+        <v>0.01610637083649635</v>
       </c>
       <c r="W20" t="n">
-        <v>0.02680009044706821</v>
+        <v>0.0003350600600242615</v>
       </c>
       <c r="X20" t="n">
-        <v>0.004868544638156891</v>
+        <v>0.0245021041482687</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.009719434194266796</v>
+        <v>0.008292598649859428</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.003615378635004163</v>
+        <v>0.006935395300388336</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.0004398580640554428</v>
+        <v>0.01725276745855808</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.00203522783704102</v>
+        <v>0.01409054268151522</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.007363473065197468</v>
+        <v>0.01894604600965977</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.0009932585526257753</v>
+        <v>0.01422743313014507</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.01017113402485847</v>
+        <v>0.003631815779954195</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.007476140279322863</v>
+        <v>0.03620696440339088</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.006316661834716797</v>
+        <v>0.03480081260204315</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.00150047882925719</v>
+        <v>0.009464241564273834</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.004303152672946453</v>
+        <v>0.04313690215349197</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.005069179460406303</v>
+        <v>0.006669532507658005</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.001620264491066337</v>
+        <v>0.00388882914558053</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.01499222312122583</v>
+        <v>0.03789063543081284</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.006326977163553238</v>
+        <v>0.007594539783895016</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.01360508985817432</v>
+        <v>0.001050589140504599</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.002340633422136307</v>
+        <v>0.06130756437778473</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.008510024286806583</v>
+        <v>0.01704290695488453</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.006050919182598591</v>
+        <v>0.01478375680744648</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.0006069489754736423</v>
+        <v>0.02316385880112648</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.0001997650979319587</v>
+        <v>0.006365567445755005</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.0004948361311107874</v>
+        <v>0.01181953214108944</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.02167940884828568</v>
+        <v>0.08526872098445892</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.005355491302907467</v>
+        <v>0.009273359552025795</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.00832027941942215</v>
+        <v>0.01862164959311485</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.03962846100330353</v>
+        <v>0.01696666143834591</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.01033537741750479</v>
+        <v>0.03101912513375282</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.009901511482894421</v>
+        <v>0.01062591001391411</v>
       </c>
       <c r="BA20" t="n">
-        <v>0.006248476915061474</v>
+        <v>0.008805877529084682</v>
       </c>
       <c r="BB20" t="n">
-        <v>0.005526914726942778</v>
+        <v>0.01423002500087023</v>
       </c>
       <c r="BC20" t="n">
-        <v>0.002285311231389642</v>
+        <v>0.01022606901824474</v>
       </c>
       <c r="BD20" t="n">
-        <v>0.0004603606648743153</v>
+        <v>0.043363306671381</v>
       </c>
       <c r="BE20" t="n">
-        <v>0.01264334563165903</v>
+        <v>0.0423211008310318</v>
       </c>
       <c r="BF20" t="n">
-        <v>0.02280539087951183</v>
+        <v>0.0169841330498457</v>
       </c>
       <c r="BG20" t="n">
-        <v>0.04522626847028732</v>
+        <v>0.05479423701763153</v>
       </c>
       <c r="BH20" t="n">
-        <v>0.0004514867905527353</v>
+        <v>0.005110902711749077</v>
       </c>
       <c r="BI20" t="n">
-        <v>0.00770110497251153</v>
+        <v>0.00397187564522028</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.01685077138245106</v>
+        <v>0.01157420501112938</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.003678599605336785</v>
+        <v>0.003523292951285839</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.008036239072680473</v>
+        <v>0.004995630122721195</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.01008350774645805</v>
+        <v>0.01537776552140713</v>
       </c>
       <c r="BN20" t="n">
-        <v>0.009946098551154137</v>
+        <v>0.001474320888519287</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.01311728917062283</v>
+        <v>0.003385287011042237</v>
       </c>
       <c r="BP20" t="n">
-        <v>0.01370138954371214</v>
+        <v>0.00630817748606205</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0.006074828561395407</v>
+        <v>0.002345444168895483</v>
       </c>
       <c r="BR20" t="n">
-        <v>0.01077057048678398</v>
+        <v>0.007127712480723858</v>
       </c>
       <c r="BS20" t="n">
-        <v>0.01346674375236034</v>
+        <v>0.02069767937064171</v>
       </c>
       <c r="BT20" t="n">
-        <v>0.0005680351750925183</v>
+        <v>0.01169918570667505</v>
       </c>
       <c r="BU20" t="n">
-        <v>0.003080518217757344</v>
+        <v>0.008289679884910583</v>
       </c>
       <c r="BV20" t="n">
-        <v>0.02176864817738533</v>
+        <v>0.05841569602489471</v>
       </c>
       <c r="BW20" t="n">
-        <v>0.004500612150877714</v>
+        <v>0.01211983058601618</v>
       </c>
       <c r="BX20" t="n">
-        <v>0.000400289602112025</v>
+        <v>0.03725704550743103</v>
       </c>
       <c r="BY20" t="n">
-        <v>0.02357691898941994</v>
+        <v>0.01284909807145596</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0.005284410435706377</v>
+        <v>0.02472180873155594</v>
       </c>
       <c r="CA20" t="n">
-        <v>0.004810811951756477</v>
+        <v>0.008267149329185486</v>
       </c>
       <c r="CB20" t="n">
-        <v>0.0001715529360808432</v>
+        <v>0.004947818350046873</v>
       </c>
       <c r="CC20" t="n">
-        <v>0.004042143933475018</v>
+        <v>0.009549472481012344</v>
       </c>
       <c r="CD20" t="n">
-        <v>0.002016685903072357</v>
+        <v>0.008990819565951824</v>
       </c>
       <c r="CE20" t="n">
-        <v>0.002192578511312604</v>
+        <v>0.04011350125074387</v>
       </c>
       <c r="CF20" t="n">
-        <v>0.007467273157089949</v>
+        <v>0.01033624447882175</v>
       </c>
       <c r="CG20" t="n">
-        <v>0.007999761961400509</v>
+        <v>0.01432418078184128</v>
       </c>
       <c r="CH20" t="n">
-        <v>0.008814679458737373</v>
+        <v>0.002844530623406172</v>
       </c>
       <c r="CI20" t="n">
-        <v>0.00186417973600328</v>
+        <v>0.01243502926081419</v>
       </c>
       <c r="CJ20" t="n">
-        <v>0.000947197200730443</v>
+        <v>0.004548699595034122</v>
       </c>
       <c r="CK20" t="n">
-        <v>0.0004857349849771708</v>
+        <v>0.009692331776022911</v>
       </c>
       <c r="CL20" t="n">
-        <v>0.002561022527515888</v>
+        <v>0.001460521365515888</v>
       </c>
       <c r="CM20" t="n">
-        <v>0.0003640632494352758</v>
+        <v>0.0172383151948452</v>
       </c>
       <c r="CN20" t="n">
-        <v>0.007351938169449568</v>
+        <v>0.03780249133706093</v>
       </c>
       <c r="CO20" t="n">
-        <v>0.002423223108053207</v>
+        <v>0.04858750104904175</v>
       </c>
       <c r="CP20" t="n">
-        <v>0.03200944885611534</v>
+        <v>0.06478752940893173</v>
       </c>
       <c r="CQ20" t="n">
-        <v>0.03149474784731865</v>
+        <v>0.03757472336292267</v>
       </c>
       <c r="CR20" t="n">
-        <v>0.005909531377255917</v>
+        <v>0.003053738735616207</v>
       </c>
       <c r="CS20" t="n">
-        <v>0.0162998866289854</v>
+        <v>0.009345851838588715</v>
       </c>
       <c r="CT20" t="n">
-        <v>0.002006105612963438</v>
+        <v>0.005615283269435167</v>
       </c>
       <c r="CU20" t="n">
-        <v>0.006170055363327265</v>
+        <v>0.01144618727266788</v>
       </c>
       <c r="CV20" t="n">
-        <v>0.002805095165967941</v>
+        <v>0.01260180491954088</v>
       </c>
       <c r="CW20" t="n">
-        <v>0.00083694834029302</v>
+        <v>0.03774196282029152</v>
       </c>
       <c r="CX20" t="n">
-        <v>0.007307462394237518</v>
+        <v>0.01098336558789015</v>
       </c>
       <c r="CY20" t="n">
-        <v>0.003365966491401196</v>
+        <v>0.01879734732210636</v>
       </c>
       <c r="CZ20" t="n">
-        <v>0.009069132618606091</v>
+        <v>0.006624005269259214</v>
       </c>
       <c r="DA20" t="n">
-        <v>0.005127304699271917</v>
+        <v>0.01315332483500242</v>
       </c>
       <c r="DB20" t="n">
-        <v>0.002358099911361933</v>
+        <v>0.003078227629885077</v>
       </c>
       <c r="DC20" t="n">
-        <v>0.0008459843811579049</v>
+        <v>0.006450362503528595</v>
       </c>
       <c r="DD20" t="n">
-        <v>0.004931782372295856</v>
+        <v>0.006205954123288393</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.001779540674760938</v>
+        <v>0.000914459815248847</v>
       </c>
       <c r="DF20" t="n">
-        <v>0.01234076917171478</v>
+        <v>0.01977795362472534</v>
       </c>
       <c r="DG20" t="n">
-        <v>0.007075993344187737</v>
+        <v>0.002231958787888288</v>
       </c>
       <c r="DH20" t="n">
-        <v>0.005452126264572144</v>
+        <v>0.03889225423336029</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.03519259765744209</v>
+        <v>0.001706237904727459</v>
       </c>
       <c r="DJ20" t="n">
-        <v>0.008428367786109447</v>
+        <v>0.04411761462688446</v>
       </c>
       <c r="DK20" t="n">
-        <v>0.01414991449564695</v>
+        <v>0.02459700778126717</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.0232841968536377</v>
+        <v>0.04481568560004234</v>
       </c>
       <c r="DM20" t="n">
-        <v>0.00948125496506691</v>
+        <v>0.005155940540134907</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.01007058657705784</v>
+        <v>0.01306522637605667</v>
       </c>
       <c r="DO20" t="n">
-        <v>0.006456479895859957</v>
+        <v>0.02001316472887993</v>
       </c>
       <c r="DP20" t="n">
-        <v>0.01376697141677141</v>
+        <v>0.003284080885350704</v>
       </c>
       <c r="DQ20" t="n">
-        <v>0.02502709813416004</v>
+        <v>0.0106909116730094</v>
       </c>
       <c r="DR20" t="n">
-        <v>0.01761998794972897</v>
+        <v>0.0107644023373723</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.0009425271418876946</v>
+        <v>0.01039545051753521</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.003581241006031632</v>
+        <v>7.510045543313026e-05</v>
       </c>
       <c r="DU20" t="n">
-        <v>0.008996397256851196</v>
+        <v>0.02827630937099457</v>
       </c>
       <c r="DV20" t="n">
-        <v>0.001334686297923326</v>
+        <v>0.03117835149168968</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.002968584420159459</v>
+        <v>0.0009821546263992786</v>
       </c>
       <c r="DX20" t="n">
-        <v>0.007684271316975355</v>
+        <v>0.004680950194597244</v>
       </c>
       <c r="DY20" t="n">
-        <v>0.006273928098380566</v>
+        <v>0.02035229094326496</v>
       </c>
       <c r="DZ20" t="n">
-        <v>0.001220782520249486</v>
+        <v>0.002805435564368963</v>
       </c>
       <c r="EA20" t="n">
-        <v>0.003512651892378926</v>
+        <v>0.0207112543284893</v>
       </c>
       <c r="EB20" t="n">
-        <v>0.01178785692900419</v>
+        <v>0.02687314338982105</v>
       </c>
       <c r="EC20" t="n">
-        <v>0.0112916836515069</v>
+        <v>0.01647531427443027</v>
       </c>
       <c r="ED20" t="n">
-        <v>0.0172226894646883</v>
+        <v>0.03520491719245911</v>
       </c>
       <c r="EE20" t="n">
-        <v>0.001450450043193996</v>
+        <v>0.03992676734924316</v>
       </c>
       <c r="EF20" t="n">
-        <v>0.002384645398706198</v>
+        <v>0.01234465278685093</v>
       </c>
       <c r="EG20" t="n">
-        <v>0.001804560655727983</v>
+        <v>0.03189500793814659</v>
       </c>
       <c r="EH20" t="n">
-        <v>0.001847232109867036</v>
+        <v>0.01124631799757481</v>
       </c>
       <c r="EI20" t="n">
-        <v>0.007626327220350504</v>
+        <v>0.003756464691832662</v>
       </c>
       <c r="EJ20" t="n">
-        <v>0.008515843190252781</v>
+        <v>0.01433478109538555</v>
       </c>
       <c r="EK20" t="n">
-        <v>0.001963167684152722</v>
+        <v>0.01911600679159164</v>
       </c>
       <c r="EL20" t="n">
-        <v>0.004535346291959286</v>
+        <v>0.002367237815633416</v>
       </c>
       <c r="EM20" t="n">
-        <v>0.003875192254781723</v>
+        <v>0.00114463665522635</v>
       </c>
       <c r="EN20" t="n">
-        <v>0.004928899928927422</v>
+        <v>0.003351144958287477</v>
       </c>
       <c r="EO20" t="n">
-        <v>0.0005894743953831494</v>
+        <v>0.006561590824276209</v>
       </c>
       <c r="EP20" t="n">
-        <v>0.004094384610652924</v>
+        <v>0.03171578049659729</v>
       </c>
       <c r="EQ20" t="n">
-        <v>0.003815934527665377</v>
+        <v>0.002552955178543925</v>
       </c>
       <c r="ER20" t="n">
-        <v>0.003594171954318881</v>
+        <v>0.01481920201331377</v>
       </c>
       <c r="ES20" t="n">
-        <v>0.002907785354182124</v>
+        <v>0.01636968739330769</v>
       </c>
       <c r="ET20" t="n">
-        <v>0.02003925479948521</v>
+        <v>0.007150815799832344</v>
       </c>
       <c r="EU20" t="n">
-        <v>0.004367796704173088</v>
+        <v>0.0001796456053853035</v>
       </c>
       <c r="EV20" t="n">
-        <v>0.001595492009073496</v>
+        <v>0.01307519152760506</v>
       </c>
       <c r="EW20" t="n">
-        <v>0.001191878225654364</v>
+        <v>0.001909684389829636</v>
       </c>
       <c r="EX20" t="n">
-        <v>0.003702521324157715</v>
+        <v>0.01131446473300457</v>
       </c>
       <c r="EY20" t="n">
-        <v>0.001872071297839284</v>
+        <v>0.04527311772108078</v>
       </c>
       <c r="EZ20" t="n">
-        <v>0.007653862237930298</v>
+        <v>0.01244199555367231</v>
       </c>
       <c r="FA20" t="n">
-        <v>0.006249615922570229</v>
+        <v>0.02495742216706276</v>
       </c>
       <c r="FB20" t="n">
-        <v>0.007100202608853579</v>
+        <v>0.005895795300602913</v>
       </c>
       <c r="FC20" t="n">
-        <v>0.003118427470326424</v>
+        <v>0.01418762933462858</v>
       </c>
       <c r="FD20" t="n">
-        <v>0.0002948454348370433</v>
+        <v>0.00455007515847683</v>
       </c>
       <c r="FE20" t="n">
-        <v>0.003595009446144104</v>
+        <v>0.01304447371512651</v>
       </c>
       <c r="FF20" t="n">
-        <v>0.002809168072417378</v>
+        <v>0.00431374553591013</v>
       </c>
       <c r="FG20" t="n">
-        <v>0.003726283088326454</v>
+        <v>0.008599963039159775</v>
       </c>
       <c r="FH20" t="n">
-        <v>0.02121712081134319</v>
+        <v>0.02786931209266186</v>
       </c>
       <c r="FI20" t="n">
-        <v>0.008365153335034847</v>
+        <v>0.01460436917841434</v>
       </c>
       <c r="FJ20" t="n">
-        <v>0.0008451670873910189</v>
+        <v>0.02744796313345432</v>
       </c>
       <c r="FK20" t="n">
-        <v>0.007234991993755102</v>
+        <v>0.003893828019499779</v>
       </c>
       <c r="FL20" t="n">
-        <v>0.001730120275169611</v>
+        <v>0.01719558425247669</v>
       </c>
       <c r="FM20" t="n">
-        <v>0.009492751210927963</v>
+        <v>0.0009703107643872499</v>
       </c>
       <c r="FN20" t="n">
-        <v>0.005629715044051409</v>
+        <v>0.02262861095368862</v>
       </c>
       <c r="FO20" t="n">
-        <v>0.002147657098248601</v>
+        <v>0.01138278469443321</v>
       </c>
       <c r="FP20" t="n">
-        <v>0.003625574987381697</v>
+        <v>0.02972887642681599</v>
       </c>
       <c r="FQ20" t="n">
-        <v>0.0155944311991334</v>
+        <v>0.05326103791594505</v>
       </c>
       <c r="FR20" t="n">
-        <v>0.005461765453219414</v>
+        <v>0.009180355817079544</v>
       </c>
       <c r="FS20" t="n">
-        <v>0.01572473160922527</v>
+        <v>0.01310100592672825</v>
       </c>
       <c r="FT20" t="n">
-        <v>0.02522667124867439</v>
+        <v>0.01593802124261856</v>
       </c>
       <c r="FU20" t="n">
-        <v>0.003314519533887506</v>
+        <v>0.0374470129609108</v>
       </c>
       <c r="FV20" t="n">
-        <v>0.0154313500970602</v>
+        <v>0.00260786572471261</v>
       </c>
       <c r="FW20" t="n">
-        <v>0.01088814344257116</v>
+        <v>0.002106451895087957</v>
       </c>
       <c r="FX20" t="n">
-        <v>0.004651794675737619</v>
+        <v>0.029932901263237</v>
       </c>
       <c r="FY20" t="n">
-        <v>0.01041767001152039</v>
+        <v>0.005386527627706528</v>
       </c>
       <c r="FZ20" t="n">
-        <v>0.003366722958162427</v>
+        <v>0.0165933221578598</v>
       </c>
       <c r="GA20" t="n">
-        <v>0.01280129700899124</v>
+        <v>0.01743961125612259</v>
       </c>
       <c r="GB20" t="n">
-        <v>0.005668715573847294</v>
+        <v>0.008595027029514313</v>
       </c>
       <c r="GC20" t="n">
-        <v>0.03148693218827248</v>
+        <v>0.0006708800792694092</v>
       </c>
       <c r="GD20" t="n">
-        <v>0.008654342964291573</v>
+        <v>0.008684122003614902</v>
       </c>
       <c r="GE20" t="n">
-        <v>0.004793319385498762</v>
+        <v>0.006519547197967768</v>
       </c>
       <c r="GF20" t="n">
-        <v>0.005207810085266829</v>
+        <v>0.02039607055485249</v>
       </c>
       <c r="GG20" t="n">
-        <v>0.00327953090891242</v>
+        <v>0.002225335687398911</v>
       </c>
     </row>
   </sheetData>
